--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30611"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F254249-DC69-49EF-953E-A9030F70A68C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0925E288-F53F-4AA6-9B8D-E7B603260FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>Fecha</t>
   </si>
@@ -81,6 +81,9 @@
     <t>Observaciones</t>
   </si>
   <si>
+    <t>Concepto</t>
+  </si>
+  <si>
     <t>Semilla</t>
   </si>
   <si>
@@ -93,25 +96,46 @@
     <t>Mercado con ruido, se ingresa a la operación asegurando un 50% y dejando correr, cierra SL positivo, se devuelve precio a Compra</t>
   </si>
   <si>
+    <t>Proteger primero: con ruido, asegurar el 50% y dejar correr; el mercado paga después.</t>
+  </si>
+  <si>
     <t>SL</t>
   </si>
   <si>
     <t>Ruido en Ventas, se asegura entrada inmediatamente queda en positivo se devuelve a SL</t>
   </si>
   <si>
+    <t>Salir en cero también es ganar: en el ruido se asegura de inmediato y, si el precio se devuelve, la gestión ya hizo su trabajo.</t>
+  </si>
+  <si>
     <t>PPA 300, SL Ahorrado</t>
   </si>
   <si>
+    <t>No operar es una operación: con PPA 300 la señal pierde su ventaja y el SL ahorrado es capital protegido.</t>
+  </si>
+  <si>
     <t>PPA 135, SL Ahorrado</t>
   </si>
   <si>
+    <t>La constancia en la regla: segundo SL ahorrado seguido (PPA 135); el filtro cuida la cuenta aunque no se vea.</t>
+  </si>
+  <si>
     <t>PA 59, TP</t>
   </si>
   <si>
+    <t>La regla se juzga en la serie, no en un día: PA 59 dejó fuera un TP que corrió hasta 1:4 y aun así se respeta el filtro.</t>
+  </si>
+  <si>
     <t>Apertura con ruido en compra, se abre la venta pero se devuelve el precio, tranquilo sin expectativa, se hacen ajustes quedan todos en protección en el retroceso de la vela</t>
   </si>
   <si>
+    <t>Operar sin expectativa: si el precio se devuelve, proteger en el retroceso de la vela y aceptar la pérdida controlada.</t>
+  </si>
+  <si>
     <t>PPA 141, se hacen 3 ajustes, por impulso se hace el tercero aunque se gano esa ultima debo respetar que maximo 2 operaciones, se hay estrategia un ajuste sino maximo 2 ajustes diarios (DISCIPLINA)</t>
+  </si>
+  <si>
+    <t>Ganar por impulso no es disciplina: el tercer ajuste salió positivo, pero el límite de 2 ajustes no se negocia.</t>
   </si>
 </sst>
 </file>
@@ -251,7 +275,16 @@
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <fill>
@@ -370,30 +403,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:O8" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14">
-  <autoFilter ref="A1:O8" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P8" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15">
+  <autoFilter ref="A1:P8" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="14"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
-    <tableColumn id="15" xr3:uid="{DD97F666-A12A-4AEC-BCDF-0D6CA1EC34DB}" name="Balance Inicial " dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{BEDB6958-2619-444F-9BA6-5C01EF5126BE}" name="Resultado" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{3D99FEEF-4BC6-4C34-8507-1BDC55D468B4}" name="Operación" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{0CB2D386-CD95-48B6-BE32-8E5E30974ED8}" name="Estrategia" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{BE561AEF-A3F1-4D70-ACEB-238E5CF316B3}" name="Ajuste 1" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{A23A4D32-0A60-4CE7-BA9E-E9240F796DA6}" name="Ajuste 2" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{DEDBB078-2359-44D8-A99F-A7DC03A35AF6}" name="Ajuste 3" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{9B01D893-46A9-4B0A-A54E-22617DD8955A}" name="Ajuste 4" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{AB48600F-4E19-42DC-A719-9A8AD9B84698}" name="Balance Final" dataDxfId="4">
+    <tableColumn id="15" xr3:uid="{DD97F666-A12A-4AEC-BCDF-0D6CA1EC34DB}" name="Balance Inicial " dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{BEDB6958-2619-444F-9BA6-5C01EF5126BE}" name="Resultado" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{3D99FEEF-4BC6-4C34-8507-1BDC55D468B4}" name="Operación" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{0CB2D386-CD95-48B6-BE32-8E5E30974ED8}" name="Estrategia" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{BE561AEF-A3F1-4D70-ACEB-238E5CF316B3}" name="Ajuste 1" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{A23A4D32-0A60-4CE7-BA9E-E9240F796DA6}" name="Ajuste 2" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{DEDBB078-2359-44D8-A99F-A7DC03A35AF6}" name="Ajuste 3" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{9B01D893-46A9-4B0A-A54E-22617DD8955A}" name="Ajuste 4" dataDxfId="6"/>
+    <tableColumn id="18" xr3:uid="{AB48600F-4E19-42DC-A719-9A8AD9B84698}" name="Balance Final" dataDxfId="5">
       <calculatedColumnFormula>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{21EF5ED0-15E1-4B6E-8A1C-92C0D27412F9}" name="Abono/Retiro" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{481EDC30-F0E0-4C13-8BD7-6FC3F7BDF3B8}" name="% día" dataDxfId="2">
+    <tableColumn id="25" xr3:uid="{21EF5ED0-15E1-4B6E-8A1C-92C0D27412F9}" name="Abono/Retiro" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{481EDC30-F0E0-4C13-8BD7-6FC3F7BDF3B8}" name="% día" dataDxfId="3">
       <calculatedColumnFormula>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{37FC7929-CC89-4264-919C-26D755C48B12}" name="% Acumulado" dataDxfId="1">
+    <tableColumn id="7" xr3:uid="{37FC7929-CC89-4264-919C-26D755C48B12}" name="% Acumulado" dataDxfId="2">
       <calculatedColumnFormula>Tabla13[[#This Row],[% día]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{258B4FD8-869C-4D06-AEC0-881ADBF62A78}" name="Observaciones" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{258B4FD8-869C-4D06-AEC0-881ADBF62A78}" name="Observaciones" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{0A710856-9F8D-4D22-98FF-8507E77747D3}" name="Concepto" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -696,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
@@ -710,10 +744,10 @@
     <col min="12" max="12" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.5703125" style="15" customWidth="1"/>
     <col min="14" max="14" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="255.7109375" style="3" customWidth="1"/>
+    <col min="15" max="16" width="23.5703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="42" customHeight="1">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="42" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -759,22 +793,25 @@
       <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="8">
         <v>46307</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="10">
         <v>520.02</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="10">
         <v>4.26</v>
@@ -796,25 +833,28 @@
         <v>0.82</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="8">
         <v>46308</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="10">
         <f>K2+L2</f>
         <v>524.28</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="10">
         <v>0</v>
@@ -837,25 +877,28 @@
         <v>0.82</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="A4" s="8">
         <v>46309</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="10">
         <f>K3+L3</f>
         <v>524.28</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
@@ -876,25 +919,28 @@
         <v>0.82</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" s="8">
         <v>46310</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="10">
         <f>K4+L4</f>
         <v>524.28</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
@@ -915,25 +961,28 @@
         <v>0.82</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" s="8">
         <v>46311</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="10">
         <f>K5+L5</f>
         <v>524.28</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
@@ -954,25 +1003,28 @@
         <v>0.82</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" s="8">
         <v>46314</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="10">
         <f>K6+L6</f>
         <v>524.28</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="10">
         <v>-5.73</v>
@@ -999,25 +1051,28 @@
         <v>-0.27292744335088137</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" s="8">
         <v>46315</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="10">
         <f>K7+L7</f>
         <v>518.54999999999995</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="10"/>
       <c r="G8" s="10">
@@ -1044,12 +1099,15 @@
         <v>-0.16879090878333725</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M1:O1048576">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="M1:P1048576">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30611"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0925E288-F53F-4AA6-9B8D-E7B603260FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A10BB0C8-924F-46E0-A7B7-3923C3E30424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
   <si>
     <t>Fecha</t>
   </si>
@@ -136,6 +136,15 @@
   </si>
   <si>
     <t>Ganar por impulso no es disciplina: el tercer ajuste salió positivo, pero el límite de 2 ajustes no se negocia.</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+  <si>
+    <t>PA 56, No se ingresa por reglas, se hace los ajustes correspondientes</t>
+  </si>
+  <si>
+    <t>Respeto mi filtro y cuido mi capital: esperar también es operar con inteligencia.</t>
   </si>
 </sst>
 </file>
@@ -403,8 +412,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P8" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15">
-  <autoFilter ref="A1:P8" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P9" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15">
+  <autoFilter ref="A1:P9" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="14"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
@@ -730,14 +739,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="10" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.140625" style="3" bestFit="1" customWidth="1"/>
@@ -1103,6 +1112,52 @@
       </c>
       <c r="P8" s="11" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10">
+        <f>K8+L8</f>
+        <v>519.08999999999992</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>520.04</v>
+      </c>
+      <c r="L9" s="10"/>
+      <c r="M9" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>0.1830125797067946</v>
+      </c>
+      <c r="N9" s="12">
+        <f>Tabla13[[#This Row],[% día]]</f>
+        <v>0.1830125797067946</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,13 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30611"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A10BB0C8-924F-46E0-A7B7-3923C3E30424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26C9A4A3-56C8-43B7-99C8-64F48BAC84CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diario Completo Leo" sheetId="4" r:id="rId1"/>
+    <sheet name="Metas" sheetId="5" r:id="rId2"/>
+    <sheet name="Riesgo" sheetId="7" state="hidden" r:id="rId3"/>
+    <sheet name="Etapas" sheetId="6" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Metas!$A$1:$J$271</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="84">
   <si>
     <t>Fecha</t>
   </si>
@@ -146,6 +152,147 @@
   <si>
     <t>Respeto mi filtro y cuido mi capital: esperar también es operar con inteligencia.</t>
   </si>
+  <si>
+    <t>Dia Semana</t>
+  </si>
+  <si>
+    <t>Dia Comienzo Meta</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>% Op. Etapa</t>
+  </si>
+  <si>
+    <t>% Esperado</t>
+  </si>
+  <si>
+    <t>% Planeado</t>
+  </si>
+  <si>
+    <t>Noticia</t>
+  </si>
+  <si>
+    <t>Nota</t>
+  </si>
+  <si>
+    <t>13:00 Federal Funds Rate, FOMC Statement, FOMC Press Conference</t>
+  </si>
+  <si>
+    <t>07:30 Advance GDP q/q, Core PCE Price Index m/m</t>
+  </si>
+  <si>
+    <t>Congressional Elections</t>
+  </si>
+  <si>
+    <t>Incubación</t>
+  </si>
+  <si>
+    <t>08:30 Average Hourly Earnings m/m, Non-Farm Employment Change, Unemployment Rate</t>
+  </si>
+  <si>
+    <t>8:30 Core CPI m/m, Core CPI y/y, CPI m/m, CPI y/y</t>
+  </si>
+  <si>
+    <t>Bank Holiday</t>
+  </si>
+  <si>
+    <t>08:30 Core PPI m/m, PPI m/m</t>
+  </si>
+  <si>
+    <t>08:30 Core Retail Sales m/m, Retail Sales m/m</t>
+  </si>
+  <si>
+    <t>14:00 FOMC Meeting Minutes</t>
+  </si>
+  <si>
+    <t>08:30 Core PCE Price Index m/m, Prelim GDP q/q</t>
+  </si>
+  <si>
+    <t>DIA DE LA SEMANA</t>
+  </si>
+  <si>
+    <t>RATIO</t>
+  </si>
+  <si>
+    <t>LUNES</t>
+  </si>
+  <si>
+    <t>MARTES</t>
+  </si>
+  <si>
+    <t>MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>JUEVES</t>
+  </si>
+  <si>
+    <t>VIERNES</t>
+  </si>
+  <si>
+    <t>SÁBADO</t>
+  </si>
+  <si>
+    <t>DOMINGO</t>
+  </si>
+  <si>
+    <t>% Op</t>
+  </si>
+  <si>
+    <t>Dias Minimos</t>
+  </si>
+  <si>
+    <t>Dias Meta</t>
+  </si>
+  <si>
+    <t>Multiplicador</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>% a Ganar</t>
+  </si>
+  <si>
+    <t>% Ganancias</t>
+  </si>
+  <si>
+    <t>Capital Personal</t>
+  </si>
+  <si>
+    <t>$500 → $1,000</t>
+  </si>
+  <si>
+    <t>$1,000 → $2,000</t>
+  </si>
+  <si>
+    <t>Aceleración</t>
+  </si>
+  <si>
+    <t>$2,000 → $5,000</t>
+  </si>
+  <si>
+    <t>Pro</t>
+  </si>
+  <si>
+    <t>$5,000 → $10,000</t>
+  </si>
+  <si>
+    <t>Pro 500</t>
+  </si>
+  <si>
+    <t>$10,000 → $20,000</t>
+  </si>
+  <si>
+    <t>Pro M</t>
+  </si>
+  <si>
+    <t>$20,000 → $1,000,000</t>
+  </si>
 </sst>
 </file>
 
@@ -155,7 +302,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +317,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -252,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -279,12 +432,41 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="26">
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <fill>
@@ -412,31 +594,89 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P9" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P9" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
   <autoFilter ref="A1:P9" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
-    <tableColumn id="15" xr3:uid="{DD97F666-A12A-4AEC-BCDF-0D6CA1EC34DB}" name="Balance Inicial " dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{BEDB6958-2619-444F-9BA6-5C01EF5126BE}" name="Resultado" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{3D99FEEF-4BC6-4C34-8507-1BDC55D468B4}" name="Operación" dataDxfId="11"/>
-    <tableColumn id="16" xr3:uid="{0CB2D386-CD95-48B6-BE32-8E5E30974ED8}" name="Estrategia" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{BE561AEF-A3F1-4D70-ACEB-238E5CF316B3}" name="Ajuste 1" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{A23A4D32-0A60-4CE7-BA9E-E9240F796DA6}" name="Ajuste 2" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{DEDBB078-2359-44D8-A99F-A7DC03A35AF6}" name="Ajuste 3" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{9B01D893-46A9-4B0A-A54E-22617DD8955A}" name="Ajuste 4" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{AB48600F-4E19-42DC-A719-9A8AD9B84698}" name="Balance Final" dataDxfId="5">
+    <tableColumn id="15" xr3:uid="{DD97F666-A12A-4AEC-BCDF-0D6CA1EC34DB}" name="Balance Inicial " dataDxfId="21"/>
+    <tableColumn id="10" xr3:uid="{BEDB6958-2619-444F-9BA6-5C01EF5126BE}" name="Resultado" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{3D99FEEF-4BC6-4C34-8507-1BDC55D468B4}" name="Operación" dataDxfId="19"/>
+    <tableColumn id="16" xr3:uid="{0CB2D386-CD95-48B6-BE32-8E5E30974ED8}" name="Estrategia" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{BE561AEF-A3F1-4D70-ACEB-238E5CF316B3}" name="Ajuste 1" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{A23A4D32-0A60-4CE7-BA9E-E9240F796DA6}" name="Ajuste 2" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{DEDBB078-2359-44D8-A99F-A7DC03A35AF6}" name="Ajuste 3" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{9B01D893-46A9-4B0A-A54E-22617DD8955A}" name="Ajuste 4" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{AB48600F-4E19-42DC-A719-9A8AD9B84698}" name="Balance Final" dataDxfId="13">
       <calculatedColumnFormula>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{21EF5ED0-15E1-4B6E-8A1C-92C0D27412F9}" name="Abono/Retiro" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{481EDC30-F0E0-4C13-8BD7-6FC3F7BDF3B8}" name="% día" dataDxfId="3">
+    <tableColumn id="25" xr3:uid="{21EF5ED0-15E1-4B6E-8A1C-92C0D27412F9}" name="Abono/Retiro" dataDxfId="12"/>
+    <tableColumn id="19" xr3:uid="{481EDC30-F0E0-4C13-8BD7-6FC3F7BDF3B8}" name="% día" dataDxfId="11">
       <calculatedColumnFormula>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{37FC7929-CC89-4264-919C-26D755C48B12}" name="% Acumulado" dataDxfId="2">
+    <tableColumn id="7" xr3:uid="{37FC7929-CC89-4264-919C-26D755C48B12}" name="% Acumulado" dataDxfId="10">
       <calculatedColumnFormula>Tabla13[[#This Row],[% día]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{258B4FD8-869C-4D06-AEC0-881ADBF62A78}" name="Observaciones" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{0A710856-9F8D-4D22-98FF-8507E77747D3}" name="Concepto" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{258B4FD8-869C-4D06-AEC0-881ADBF62A78}" name="Observaciones" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{0A710856-9F8D-4D22-98FF-8507E77747D3}" name="Concepto" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2156171D-F1A5-4828-A6FD-02ECC9AAE303}" name="Tabla3" displayName="Tabla3" ref="A1:J271" totalsRowShown="0">
+  <autoFilter ref="A1:J271" xr:uid="{2156171D-F1A5-4828-A6FD-02ECC9AAE303}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{AC54A394-CDAC-4B1B-BB40-28A5F8B2333E}" name="Fecha" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{BA0D5A4F-1869-4623-8ACF-8E7166F1692C}" name="Dia Semana">
+      <calculatedColumnFormula>UPPER(TEXT(A2,"dddd"))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{61EBBFB8-9CD9-4F46-A9E9-3872EB53E421}" name="Dia Comienzo Meta"/>
+    <tableColumn id="4" xr3:uid="{DEF367B4-2605-44E9-A966-E51183A30A9E}" name="Ratio" dataDxfId="6">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{42B1688E-B917-4CEA-9A1D-F4D0047D5D52}" name="Etapa"/>
+    <tableColumn id="6" xr3:uid="{CD0EA086-03B3-4870-BA83-709EC375B9E7}" name="% Op. Etapa" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{AD9AEAAB-65D2-42CD-B37A-280E09265EFE}" name="% Esperado" dataDxfId="4">
+      <calculatedColumnFormula>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{A13F701D-283F-495D-8FD6-00681E1504A2}" name="% Planeado" dataDxfId="3">
+      <calculatedColumnFormula>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{F8209525-F89B-42F6-97F8-05BDD66A1611}" name="Noticia"/>
+    <tableColumn id="10" xr3:uid="{EAB9AF61-4AF0-4E26-8407-039266DEE226}" name="Nota"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0270FA24-DF24-43D8-93D9-D514CC1F7599}" name="Tabla4" displayName="Tabla4" ref="A1:B8" totalsRowShown="0">
+  <autoFilter ref="A1:B8" xr:uid="{0270FA24-DF24-43D8-93D9-D514CC1F7599}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{85372D3E-3FA5-47F3-BBF4-C87C1A63E8CE}" name="DIA DE LA SEMANA"/>
+    <tableColumn id="2" xr3:uid="{569520CF-B8A0-437A-A03B-331CE042FC85}" name="RATIO"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9351767B-1ACF-4E39-852C-4C842012EA80}" name="Tabla1" displayName="Tabla1" ref="A1:I7" totalsRowShown="0">
+  <autoFilter ref="A1:I7" xr:uid="{9351767B-1ACF-4E39-852C-4C842012EA80}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{960F446E-BFA4-457E-9A5C-C644287A6FE8}" name="Etapa"/>
+    <tableColumn id="9" xr3:uid="{4BA45E59-386E-4AF3-8AA3-25BD6C26B760}" name="% Op" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{19AC0693-5D31-44DB-B7CA-C236F7AEB1A4}" name="Dias Minimos"/>
+    <tableColumn id="2" xr3:uid="{77A31CBB-26F3-4537-9F50-FEED10EC862C}" name="Dias Meta"/>
+    <tableColumn id="3" xr3:uid="{6B24B6E5-C8BA-492C-8753-A2EB20EEDED9}" name="Multiplicador"/>
+    <tableColumn id="4" xr3:uid="{EFB293A9-C1AB-4E41-BA32-617BA402D612}" name="Edge"/>
+    <tableColumn id="5" xr3:uid="{88EC99F6-4877-4F98-8E5D-0F9EB897E1B7}" name="% a Ganar" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{5FDF6862-E9EE-4B81-9E4C-56DA35040979}" name="% Ganancias" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{24013E9D-98D1-4774-BFD5-CAC8AE44779F}" name="Capital Personal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1162,7 +1402,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1170,5 +1410,9011 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2B951085-2B89-4222-A00A-EC824C40CDB9}">
+          <x14:formula1>
+            <xm:f>Etapas!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B9</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A1D044E-337F-4736-9478-06CE436A3C4E}">
+  <dimension ref="A1:J271"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" customWidth="1"/>
+    <col min="6" max="7" width="7.28515625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="6" style="17" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="18">
+        <v>46317</v>
+      </c>
+      <c r="B2" t="str">
+        <f t="shared" ref="B2:B65" si="0">UPPER(TEXT(A2,"dddd"))</f>
+        <v>JUEVES</v>
+      </c>
+      <c r="C2">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G2" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="H2" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.04</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="18">
+        <v>46318</v>
+      </c>
+      <c r="B3" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C3">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G3" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.02</v>
+      </c>
+      <c r="H3" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.02</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="18">
+        <v>46319</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C4">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G4" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="18">
+        <v>46320</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G5" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="18">
+        <v>46321</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G6" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="H6" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.04</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="18">
+        <v>46322</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G7" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="H7" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.04</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="18">
+        <v>46323</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G8" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.02</v>
+      </c>
+      <c r="H8" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="18">
+        <v>46324</v>
+      </c>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C9">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G9" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="H9" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.02</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="18">
+        <v>46325</v>
+      </c>
+      <c r="B10" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C10">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G10" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.02</v>
+      </c>
+      <c r="H10" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.02</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="18">
+        <v>46326</v>
+      </c>
+      <c r="B11" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C11">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G11" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="18">
+        <v>46327</v>
+      </c>
+      <c r="B12" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C12">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G12" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="18">
+        <v>46328</v>
+      </c>
+      <c r="B13" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C13">
+        <v>27</v>
+      </c>
+      <c r="D13">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G13" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="H13" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.04</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="18">
+        <v>46329</v>
+      </c>
+      <c r="B14" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C14">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G14" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="H14" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.02</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="18">
+        <v>46330</v>
+      </c>
+      <c r="B15" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C15">
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G15" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.02</v>
+      </c>
+      <c r="H15" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.02</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="18">
+        <v>46331</v>
+      </c>
+      <c r="B16" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C16">
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G16" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.04</v>
+      </c>
+      <c r="H16" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.04</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="18">
+        <v>46332</v>
+      </c>
+      <c r="B17" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C17">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G17" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H17" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="18">
+        <v>46333</v>
+      </c>
+      <c r="B18" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C18">
+        <v>32</v>
+      </c>
+      <c r="D18">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G18" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="18">
+        <v>46334</v>
+      </c>
+      <c r="B19" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C19">
+        <v>33</v>
+      </c>
+      <c r="D19">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G19" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="18">
+        <v>46335</v>
+      </c>
+      <c r="B20" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C20">
+        <v>34</v>
+      </c>
+      <c r="D20">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G20" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H20" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="18">
+        <v>46336</v>
+      </c>
+      <c r="B21" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C21">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G21" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H21" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="18">
+        <v>46337</v>
+      </c>
+      <c r="B22" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C22">
+        <v>36</v>
+      </c>
+      <c r="D22">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G22" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H22" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="18">
+        <v>46338</v>
+      </c>
+      <c r="B23" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C23">
+        <v>37</v>
+      </c>
+      <c r="D23">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G23" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H23" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="18">
+        <v>46339</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C24">
+        <v>38</v>
+      </c>
+      <c r="D24">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G24" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H24" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="18">
+        <v>46340</v>
+      </c>
+      <c r="B25" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C25">
+        <v>39</v>
+      </c>
+      <c r="D25">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G25" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="18">
+        <v>46341</v>
+      </c>
+      <c r="B26" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C26">
+        <v>40</v>
+      </c>
+      <c r="D26">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G26" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="18">
+        <v>46342</v>
+      </c>
+      <c r="B27" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C27">
+        <v>41</v>
+      </c>
+      <c r="D27">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G27" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H27" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="18">
+        <v>46343</v>
+      </c>
+      <c r="B28" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C28">
+        <v>42</v>
+      </c>
+      <c r="D28">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G28" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H28" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="18">
+        <v>46344</v>
+      </c>
+      <c r="B29" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C29">
+        <v>43</v>
+      </c>
+      <c r="D29">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G29" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H29" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="18">
+        <v>46345</v>
+      </c>
+      <c r="B30" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C30">
+        <v>44</v>
+      </c>
+      <c r="D30">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G30" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H30" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="18">
+        <v>46346</v>
+      </c>
+      <c r="B31" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C31">
+        <v>45</v>
+      </c>
+      <c r="D31">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G31" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H31" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="18">
+        <v>46347</v>
+      </c>
+      <c r="B32" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C32">
+        <v>46</v>
+      </c>
+      <c r="D32">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G32" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" s="18">
+        <v>46348</v>
+      </c>
+      <c r="B33" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C33">
+        <v>47</v>
+      </c>
+      <c r="D33">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G33" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="18">
+        <v>46349</v>
+      </c>
+      <c r="B34" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C34">
+        <v>48</v>
+      </c>
+      <c r="D34">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G34" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H34" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="18">
+        <v>46350</v>
+      </c>
+      <c r="B35" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C35">
+        <v>49</v>
+      </c>
+      <c r="D35">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G35" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H35" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="18">
+        <v>46351</v>
+      </c>
+      <c r="B36" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C36">
+        <v>50</v>
+      </c>
+      <c r="D36">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G36" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H36" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="18">
+        <v>46352</v>
+      </c>
+      <c r="B37" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C37">
+        <v>51</v>
+      </c>
+      <c r="D37">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G37" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H37" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="18">
+        <v>46353</v>
+      </c>
+      <c r="B38" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C38">
+        <v>52</v>
+      </c>
+      <c r="D38">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G38" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H38" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="18">
+        <v>46354</v>
+      </c>
+      <c r="B39" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C39">
+        <v>53</v>
+      </c>
+      <c r="D39">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G39" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="18">
+        <v>46355</v>
+      </c>
+      <c r="B40" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C40">
+        <v>54</v>
+      </c>
+      <c r="D40">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G40" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="18">
+        <v>46356</v>
+      </c>
+      <c r="B41" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C41">
+        <v>55</v>
+      </c>
+      <c r="D41">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G41" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H41" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="18">
+        <v>46357</v>
+      </c>
+      <c r="B42" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C42">
+        <v>56</v>
+      </c>
+      <c r="D42">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G42" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H42" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="18">
+        <v>46358</v>
+      </c>
+      <c r="B43" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C43">
+        <v>57</v>
+      </c>
+      <c r="D43">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G43" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H43" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="18">
+        <v>46359</v>
+      </c>
+      <c r="B44" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C44">
+        <v>58</v>
+      </c>
+      <c r="D44">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G44" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H44" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="18">
+        <v>46360</v>
+      </c>
+      <c r="B45" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C45">
+        <v>59</v>
+      </c>
+      <c r="D45">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G45" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H45" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="18">
+        <v>46361</v>
+      </c>
+      <c r="B46" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C46">
+        <v>60</v>
+      </c>
+      <c r="D46">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G46" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="18">
+        <v>46362</v>
+      </c>
+      <c r="B47" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C47">
+        <v>61</v>
+      </c>
+      <c r="D47">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G47" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H47" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="18">
+        <v>46363</v>
+      </c>
+      <c r="B48" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C48">
+        <v>62</v>
+      </c>
+      <c r="D48">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F48" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G48" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H48" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="18">
+        <v>46364</v>
+      </c>
+      <c r="B49" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C49">
+        <v>63</v>
+      </c>
+      <c r="D49">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G49" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H49" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="18">
+        <v>46365</v>
+      </c>
+      <c r="B50" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C50">
+        <v>64</v>
+      </c>
+      <c r="D50">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
+        <v>49</v>
+      </c>
+      <c r="F50" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G50" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H50" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="18">
+        <v>46366</v>
+      </c>
+      <c r="B51" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C51">
+        <v>65</v>
+      </c>
+      <c r="D51">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E51" t="s">
+        <v>49</v>
+      </c>
+      <c r="F51" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G51" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H51" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="18">
+        <v>46367</v>
+      </c>
+      <c r="B52" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C52">
+        <v>66</v>
+      </c>
+      <c r="D52">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>49</v>
+      </c>
+      <c r="F52" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G52" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H52" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="18">
+        <v>46368</v>
+      </c>
+      <c r="B53" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C53">
+        <v>67</v>
+      </c>
+      <c r="D53">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>49</v>
+      </c>
+      <c r="F53" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G53" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="18">
+        <v>46369</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C54">
+        <v>68</v>
+      </c>
+      <c r="D54">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G54" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="18">
+        <v>46370</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C55">
+        <v>69</v>
+      </c>
+      <c r="D55">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G55" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H55" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="18">
+        <v>46371</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C56">
+        <v>70</v>
+      </c>
+      <c r="D56">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>49</v>
+      </c>
+      <c r="F56" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G56" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H56" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="18">
+        <v>46372</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C57">
+        <v>71</v>
+      </c>
+      <c r="D57">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G57" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H57" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="18">
+        <v>46373</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C58">
+        <v>72</v>
+      </c>
+      <c r="D58">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E58" t="s">
+        <v>49</v>
+      </c>
+      <c r="F58" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G58" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H58" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="18">
+        <v>46374</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="0"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C59">
+        <v>73</v>
+      </c>
+      <c r="D59">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>49</v>
+      </c>
+      <c r="F59" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G59" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H59" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="18">
+        <v>46375</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="0"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C60">
+        <v>74</v>
+      </c>
+      <c r="D60">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G60" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="18">
+        <v>46376</v>
+      </c>
+      <c r="B61" t="str">
+        <f t="shared" si="0"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C61">
+        <v>75</v>
+      </c>
+      <c r="D61">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E61" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G61" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H61" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="18">
+        <v>46377</v>
+      </c>
+      <c r="B62" t="str">
+        <f t="shared" si="0"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C62">
+        <v>76</v>
+      </c>
+      <c r="D62">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E62" t="s">
+        <v>49</v>
+      </c>
+      <c r="F62" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G62" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H62" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="18">
+        <v>46378</v>
+      </c>
+      <c r="B63" t="str">
+        <f t="shared" si="0"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C63">
+        <v>77</v>
+      </c>
+      <c r="D63">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E63" t="s">
+        <v>49</v>
+      </c>
+      <c r="F63" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G63" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H63" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="18">
+        <v>46379</v>
+      </c>
+      <c r="B64" t="str">
+        <f t="shared" si="0"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C64">
+        <v>78</v>
+      </c>
+      <c r="D64">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G64" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H64" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="18">
+        <v>46380</v>
+      </c>
+      <c r="B65" t="str">
+        <f t="shared" si="0"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C65">
+        <v>79</v>
+      </c>
+      <c r="D65">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>49</v>
+      </c>
+      <c r="F65" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G65" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H65" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="18">
+        <v>46381</v>
+      </c>
+      <c r="B66" t="str">
+        <f t="shared" ref="B66:B129" si="1">UPPER(TEXT(A66,"dddd"))</f>
+        <v>VIERNES</v>
+      </c>
+      <c r="C66">
+        <v>80</v>
+      </c>
+      <c r="D66">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E66" t="s">
+        <v>49</v>
+      </c>
+      <c r="F66" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G66" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H66" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" s="18">
+        <v>46382</v>
+      </c>
+      <c r="B67" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C67">
+        <v>81</v>
+      </c>
+      <c r="D67">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E67" t="s">
+        <v>49</v>
+      </c>
+      <c r="F67" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G67" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H67" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" s="18">
+        <v>46383</v>
+      </c>
+      <c r="B68" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C68">
+        <v>82</v>
+      </c>
+      <c r="D68">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="E68" t="s">
+        <v>49</v>
+      </c>
+      <c r="F68" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G68" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" s="18">
+        <v>46384</v>
+      </c>
+      <c r="B69" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C69">
+        <v>83</v>
+      </c>
+      <c r="D69">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E69" t="s">
+        <v>49</v>
+      </c>
+      <c r="F69" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G69" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H69" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" s="18">
+        <v>46385</v>
+      </c>
+      <c r="B70" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C70">
+        <v>84</v>
+      </c>
+      <c r="D70">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E70" t="s">
+        <v>49</v>
+      </c>
+      <c r="F70" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G70" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H70" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="18">
+        <v>46386</v>
+      </c>
+      <c r="B71" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C71">
+        <v>85</v>
+      </c>
+      <c r="D71">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>49</v>
+      </c>
+      <c r="F71" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G71" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H71" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="18">
+        <v>46387</v>
+      </c>
+      <c r="B72" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C72">
+        <v>86</v>
+      </c>
+      <c r="D72">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="E72" t="s">
+        <v>49</v>
+      </c>
+      <c r="F72" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G72" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0.01</v>
+      </c>
+      <c r="H72" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0.01</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="18">
+        <v>46388</v>
+      </c>
+      <c r="B73" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C73">
+        <v>87</v>
+      </c>
+      <c r="D73">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F73" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="18">
+        <v>46389</v>
+      </c>
+      <c r="B74" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C74">
+        <v>88</v>
+      </c>
+      <c r="D74">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G74" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H74" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="18">
+        <v>46390</v>
+      </c>
+      <c r="B75" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C75">
+        <v>89</v>
+      </c>
+      <c r="D75">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F75" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G75" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H75" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="18">
+        <v>46391</v>
+      </c>
+      <c r="B76" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C76">
+        <v>90</v>
+      </c>
+      <c r="D76">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F76" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G76" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H76" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="18">
+        <v>46392</v>
+      </c>
+      <c r="B77" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C77">
+        <v>91</v>
+      </c>
+      <c r="D77">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F77" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G77" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H77" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="18">
+        <v>46393</v>
+      </c>
+      <c r="B78" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C78">
+        <v>92</v>
+      </c>
+      <c r="D78">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F78" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G78" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H78" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="18">
+        <v>46394</v>
+      </c>
+      <c r="B79" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C79">
+        <v>93</v>
+      </c>
+      <c r="D79">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F79" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G79" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="18">
+        <v>46395</v>
+      </c>
+      <c r="B80" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C80">
+        <v>94</v>
+      </c>
+      <c r="D80">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F80" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G80" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H80" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="18">
+        <v>46396</v>
+      </c>
+      <c r="B81" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C81">
+        <v>95</v>
+      </c>
+      <c r="D81">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G81" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="18">
+        <v>46397</v>
+      </c>
+      <c r="B82" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C82">
+        <v>96</v>
+      </c>
+      <c r="D82">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="18">
+        <v>46398</v>
+      </c>
+      <c r="B83" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C83">
+        <v>97</v>
+      </c>
+      <c r="D83">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F83" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G83" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="18">
+        <v>46399</v>
+      </c>
+      <c r="B84" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C84">
+        <v>98</v>
+      </c>
+      <c r="D84">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F84" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="18">
+        <v>46400</v>
+      </c>
+      <c r="B85" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C85">
+        <v>99</v>
+      </c>
+      <c r="D85">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F85" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G85" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="18">
+        <v>46401</v>
+      </c>
+      <c r="B86" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C86">
+        <v>100</v>
+      </c>
+      <c r="D86">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F86" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G86" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="18">
+        <v>46402</v>
+      </c>
+      <c r="B87" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C87">
+        <v>101</v>
+      </c>
+      <c r="D87">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F87" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G87" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H87" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="18">
+        <v>46403</v>
+      </c>
+      <c r="B88" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C88">
+        <v>102</v>
+      </c>
+      <c r="D88">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F88" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G88" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H88" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="18">
+        <v>46404</v>
+      </c>
+      <c r="B89" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C89">
+        <v>103</v>
+      </c>
+      <c r="D89">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G89" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H89" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="18">
+        <v>46405</v>
+      </c>
+      <c r="B90" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C90">
+        <v>104</v>
+      </c>
+      <c r="D90">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F90" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G90" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H90" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="18">
+        <v>46406</v>
+      </c>
+      <c r="B91" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C91">
+        <v>105</v>
+      </c>
+      <c r="D91">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F91" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H91" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="18">
+        <v>46407</v>
+      </c>
+      <c r="B92" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C92">
+        <v>106</v>
+      </c>
+      <c r="D92">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F92" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H92" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="18">
+        <v>46408</v>
+      </c>
+      <c r="B93" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C93">
+        <v>107</v>
+      </c>
+      <c r="D93">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F93" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G93" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H93" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="18">
+        <v>46409</v>
+      </c>
+      <c r="B94" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C94">
+        <v>108</v>
+      </c>
+      <c r="D94">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F94" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="18">
+        <v>46410</v>
+      </c>
+      <c r="B95" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C95">
+        <v>109</v>
+      </c>
+      <c r="D95">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G95" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="18">
+        <v>46411</v>
+      </c>
+      <c r="B96" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C96">
+        <v>110</v>
+      </c>
+      <c r="D96">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F96" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G96" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H96" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" s="18">
+        <v>46412</v>
+      </c>
+      <c r="B97" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C97">
+        <v>111</v>
+      </c>
+      <c r="D97">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F97" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G97" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H97" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" s="18">
+        <v>46413</v>
+      </c>
+      <c r="B98" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C98">
+        <v>112</v>
+      </c>
+      <c r="D98">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F98" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G98" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H98" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" s="18">
+        <v>46414</v>
+      </c>
+      <c r="B99" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C99">
+        <v>113</v>
+      </c>
+      <c r="D99">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F99" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G99" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H99" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" s="18">
+        <v>46415</v>
+      </c>
+      <c r="B100" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C100">
+        <v>114</v>
+      </c>
+      <c r="D100">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F100" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G100" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H100" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" s="18">
+        <v>46416</v>
+      </c>
+      <c r="B101" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C101">
+        <v>115</v>
+      </c>
+      <c r="D101">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F101" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G101" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H101" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" s="18">
+        <v>46417</v>
+      </c>
+      <c r="B102" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C102">
+        <v>116</v>
+      </c>
+      <c r="D102">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G102" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H102" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="18">
+        <v>46418</v>
+      </c>
+      <c r="B103" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C103">
+        <v>117</v>
+      </c>
+      <c r="D103">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G103" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="18">
+        <v>46419</v>
+      </c>
+      <c r="B104" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C104">
+        <v>118</v>
+      </c>
+      <c r="D104">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F104" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="18">
+        <v>46420</v>
+      </c>
+      <c r="B105" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C105">
+        <v>119</v>
+      </c>
+      <c r="D105">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F105" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G105" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="18">
+        <v>46421</v>
+      </c>
+      <c r="B106" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C106">
+        <v>120</v>
+      </c>
+      <c r="D106">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F106" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G106" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H106" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="18">
+        <v>46422</v>
+      </c>
+      <c r="B107" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C107">
+        <v>121</v>
+      </c>
+      <c r="D107">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F107" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G107" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H107" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="18">
+        <v>46423</v>
+      </c>
+      <c r="B108" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C108">
+        <v>122</v>
+      </c>
+      <c r="D108">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F108" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G108" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H108" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="18">
+        <v>46424</v>
+      </c>
+      <c r="B109" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C109">
+        <v>123</v>
+      </c>
+      <c r="D109">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F109" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G109" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H109" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="18">
+        <v>46425</v>
+      </c>
+      <c r="B110" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C110">
+        <v>124</v>
+      </c>
+      <c r="D110">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F110" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G110" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H110" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="18">
+        <v>46426</v>
+      </c>
+      <c r="B111" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C111">
+        <v>125</v>
+      </c>
+      <c r="D111">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F111" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G111" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="18">
+        <v>46427</v>
+      </c>
+      <c r="B112" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C112">
+        <v>126</v>
+      </c>
+      <c r="D112">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F112" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G112" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H112" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="18">
+        <v>46428</v>
+      </c>
+      <c r="B113" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C113">
+        <v>127</v>
+      </c>
+      <c r="D113">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F113" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G113" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H113" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="18">
+        <v>46429</v>
+      </c>
+      <c r="B114" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C114">
+        <v>128</v>
+      </c>
+      <c r="D114">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F114" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G114" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="18">
+        <v>46430</v>
+      </c>
+      <c r="B115" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C115">
+        <v>129</v>
+      </c>
+      <c r="D115">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F115" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G115" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H115" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="18">
+        <v>46431</v>
+      </c>
+      <c r="B116" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C116">
+        <v>130</v>
+      </c>
+      <c r="D116">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F116" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G116" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H116" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="18">
+        <v>46432</v>
+      </c>
+      <c r="B117" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C117">
+        <v>131</v>
+      </c>
+      <c r="D117">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F117" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G117" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H117" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="18">
+        <v>46433</v>
+      </c>
+      <c r="B118" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C118">
+        <v>132</v>
+      </c>
+      <c r="D118">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F118" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G118" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H118" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="18">
+        <v>46434</v>
+      </c>
+      <c r="B119" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C119">
+        <v>133</v>
+      </c>
+      <c r="D119">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F119" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G119" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H119" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="18">
+        <v>46435</v>
+      </c>
+      <c r="B120" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C120">
+        <v>134</v>
+      </c>
+      <c r="D120">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F120" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G120" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H120" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="18">
+        <v>46436</v>
+      </c>
+      <c r="B121" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C121">
+        <v>135</v>
+      </c>
+      <c r="D121">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F121" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G121" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H121" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="18">
+        <v>46437</v>
+      </c>
+      <c r="B122" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C122">
+        <v>136</v>
+      </c>
+      <c r="D122">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F122" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G122" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H122" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="18">
+        <v>46438</v>
+      </c>
+      <c r="B123" t="str">
+        <f t="shared" si="1"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C123">
+        <v>137</v>
+      </c>
+      <c r="D123">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F123" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G123" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H123" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="18">
+        <v>46439</v>
+      </c>
+      <c r="B124" t="str">
+        <f t="shared" si="1"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C124">
+        <v>138</v>
+      </c>
+      <c r="D124">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F124" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G124" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H124" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="18">
+        <v>46440</v>
+      </c>
+      <c r="B125" t="str">
+        <f t="shared" si="1"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C125">
+        <v>139</v>
+      </c>
+      <c r="D125">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F125" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G125" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H125" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="18">
+        <v>46441</v>
+      </c>
+      <c r="B126" t="str">
+        <f t="shared" si="1"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C126">
+        <v>140</v>
+      </c>
+      <c r="D126">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F126" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G126" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H126" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="18">
+        <v>46442</v>
+      </c>
+      <c r="B127" t="str">
+        <f t="shared" si="1"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C127">
+        <v>141</v>
+      </c>
+      <c r="D127">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F127" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G127" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H127" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="18">
+        <v>46443</v>
+      </c>
+      <c r="B128" t="str">
+        <f t="shared" si="1"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C128">
+        <v>142</v>
+      </c>
+      <c r="D128">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F128" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G128" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H128" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="18">
+        <v>46444</v>
+      </c>
+      <c r="B129" t="str">
+        <f t="shared" si="1"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C129">
+        <v>143</v>
+      </c>
+      <c r="D129">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F129" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G129" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H129" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="18">
+        <v>46445</v>
+      </c>
+      <c r="B130" t="str">
+        <f t="shared" ref="B130:B193" si="2">UPPER(TEXT(A130,"dddd"))</f>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C130">
+        <v>144</v>
+      </c>
+      <c r="D130">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F130" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G130" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H130" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="18">
+        <v>46446</v>
+      </c>
+      <c r="B131" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C131">
+        <v>145</v>
+      </c>
+      <c r="D131">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F131" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G131" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H131" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="18">
+        <v>46447</v>
+      </c>
+      <c r="B132" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C132">
+        <v>146</v>
+      </c>
+      <c r="D132">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F132" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G132" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H132" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="18">
+        <v>46448</v>
+      </c>
+      <c r="B133" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C133">
+        <v>147</v>
+      </c>
+      <c r="D133">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F133" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G133" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H133" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="18">
+        <v>46449</v>
+      </c>
+      <c r="B134" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C134">
+        <v>148</v>
+      </c>
+      <c r="D134">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F134" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G134" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H134" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" s="18">
+        <v>46450</v>
+      </c>
+      <c r="B135" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C135">
+        <v>149</v>
+      </c>
+      <c r="D135">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F135" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G135" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H135" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" s="18">
+        <v>46451</v>
+      </c>
+      <c r="B136" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C136">
+        <v>150</v>
+      </c>
+      <c r="D136">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F136" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G136" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H136" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" s="18">
+        <v>46452</v>
+      </c>
+      <c r="B137" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C137">
+        <v>151</v>
+      </c>
+      <c r="D137">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F137" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G137" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H137" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" s="18">
+        <v>46453</v>
+      </c>
+      <c r="B138" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C138">
+        <v>152</v>
+      </c>
+      <c r="D138">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F138" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G138" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H138" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" s="18">
+        <v>46454</v>
+      </c>
+      <c r="B139" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C139">
+        <v>153</v>
+      </c>
+      <c r="D139">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F139" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G139" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H139" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" s="18">
+        <v>46455</v>
+      </c>
+      <c r="B140" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C140">
+        <v>154</v>
+      </c>
+      <c r="D140">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F140" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G140" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H140" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" s="18">
+        <v>46456</v>
+      </c>
+      <c r="B141" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C141">
+        <v>155</v>
+      </c>
+      <c r="D141">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F141" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G141" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H141" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" s="18">
+        <v>46457</v>
+      </c>
+      <c r="B142" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C142">
+        <v>156</v>
+      </c>
+      <c r="D142">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F142" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G142" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H142" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" s="18">
+        <v>46458</v>
+      </c>
+      <c r="B143" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C143">
+        <v>157</v>
+      </c>
+      <c r="D143">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F143" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G143" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H143" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" s="18">
+        <v>46459</v>
+      </c>
+      <c r="B144" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C144">
+        <v>158</v>
+      </c>
+      <c r="D144">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F144" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G144" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H144" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" s="18">
+        <v>46460</v>
+      </c>
+      <c r="B145" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C145">
+        <v>159</v>
+      </c>
+      <c r="D145">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F145" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G145" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H145" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" s="18">
+        <v>46461</v>
+      </c>
+      <c r="B146" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C146">
+        <v>160</v>
+      </c>
+      <c r="D146">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F146" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G146" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H146" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" s="18">
+        <v>46462</v>
+      </c>
+      <c r="B147" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C147">
+        <v>161</v>
+      </c>
+      <c r="D147">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F147" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G147" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H147" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" s="18">
+        <v>46463</v>
+      </c>
+      <c r="B148" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C148">
+        <v>162</v>
+      </c>
+      <c r="D148">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F148" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G148" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H148" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" s="18">
+        <v>46464</v>
+      </c>
+      <c r="B149" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C149">
+        <v>163</v>
+      </c>
+      <c r="D149">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F149" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G149" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H149" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" s="18">
+        <v>46465</v>
+      </c>
+      <c r="B150" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C150">
+        <v>164</v>
+      </c>
+      <c r="D150">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F150" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G150" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H150" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="18">
+        <v>46466</v>
+      </c>
+      <c r="B151" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C151">
+        <v>165</v>
+      </c>
+      <c r="D151">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F151" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G151" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H151" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" s="18">
+        <v>46467</v>
+      </c>
+      <c r="B152" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C152">
+        <v>166</v>
+      </c>
+      <c r="D152">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F152" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G152" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H152" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" s="18">
+        <v>46468</v>
+      </c>
+      <c r="B153" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C153">
+        <v>167</v>
+      </c>
+      <c r="D153">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F153" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G153" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H153" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" s="18">
+        <v>46469</v>
+      </c>
+      <c r="B154" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C154">
+        <v>168</v>
+      </c>
+      <c r="D154">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F154" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G154" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H154" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" s="18">
+        <v>46470</v>
+      </c>
+      <c r="B155" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C155">
+        <v>169</v>
+      </c>
+      <c r="D155">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F155" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G155" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H155" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" s="18">
+        <v>46471</v>
+      </c>
+      <c r="B156" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C156">
+        <v>170</v>
+      </c>
+      <c r="D156">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F156" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G156" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H156" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" s="18">
+        <v>46472</v>
+      </c>
+      <c r="B157" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C157">
+        <v>171</v>
+      </c>
+      <c r="D157">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F157" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G157" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H157" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" s="18">
+        <v>46473</v>
+      </c>
+      <c r="B158" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C158">
+        <v>172</v>
+      </c>
+      <c r="D158">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F158" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G158" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H158" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" s="18">
+        <v>46474</v>
+      </c>
+      <c r="B159" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C159">
+        <v>173</v>
+      </c>
+      <c r="D159">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F159" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G159" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H159" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" s="18">
+        <v>46475</v>
+      </c>
+      <c r="B160" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C160">
+        <v>174</v>
+      </c>
+      <c r="D160">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F160" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G160" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H160" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" s="18">
+        <v>46476</v>
+      </c>
+      <c r="B161" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C161">
+        <v>175</v>
+      </c>
+      <c r="D161">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F161" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G161" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H161" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" s="18">
+        <v>46477</v>
+      </c>
+      <c r="B162" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C162">
+        <v>176</v>
+      </c>
+      <c r="D162">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F162" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G162" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H162" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" s="18">
+        <v>46478</v>
+      </c>
+      <c r="B163" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C163">
+        <v>177</v>
+      </c>
+      <c r="D163">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F163" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G163" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H163" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" s="18">
+        <v>46479</v>
+      </c>
+      <c r="B164" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C164">
+        <v>178</v>
+      </c>
+      <c r="D164">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F164" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G164" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H164" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" s="18">
+        <v>46480</v>
+      </c>
+      <c r="B165" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C165">
+        <v>179</v>
+      </c>
+      <c r="D165">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F165" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G165" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H165" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" s="18">
+        <v>46481</v>
+      </c>
+      <c r="B166" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C166">
+        <v>180</v>
+      </c>
+      <c r="D166">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F166" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G166" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H166" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" s="18">
+        <v>46482</v>
+      </c>
+      <c r="B167" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C167">
+        <v>181</v>
+      </c>
+      <c r="D167">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F167" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G167" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H167" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" s="18">
+        <v>46483</v>
+      </c>
+      <c r="B168" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C168">
+        <v>182</v>
+      </c>
+      <c r="D168">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F168" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G168" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H168" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" s="18">
+        <v>46484</v>
+      </c>
+      <c r="B169" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C169">
+        <v>183</v>
+      </c>
+      <c r="D169">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F169" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G169" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H169" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" s="18">
+        <v>46485</v>
+      </c>
+      <c r="B170" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C170">
+        <v>184</v>
+      </c>
+      <c r="D170">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F170" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G170" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H170" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" s="18">
+        <v>46486</v>
+      </c>
+      <c r="B171" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C171">
+        <v>185</v>
+      </c>
+      <c r="D171">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F171" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G171" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H171" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" s="18">
+        <v>46487</v>
+      </c>
+      <c r="B172" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C172">
+        <v>186</v>
+      </c>
+      <c r="D172">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F172" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G172" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H172" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" s="18">
+        <v>46488</v>
+      </c>
+      <c r="B173" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C173">
+        <v>187</v>
+      </c>
+      <c r="D173">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F173" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G173" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H173" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" s="18">
+        <v>46489</v>
+      </c>
+      <c r="B174" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C174">
+        <v>188</v>
+      </c>
+      <c r="D174">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F174" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G174" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H174" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" s="18">
+        <v>46490</v>
+      </c>
+      <c r="B175" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C175">
+        <v>189</v>
+      </c>
+      <c r="D175">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F175" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G175" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H175" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" s="18">
+        <v>46491</v>
+      </c>
+      <c r="B176" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C176">
+        <v>190</v>
+      </c>
+      <c r="D176">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F176" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G176" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H176" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" s="18">
+        <v>46492</v>
+      </c>
+      <c r="B177" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C177">
+        <v>191</v>
+      </c>
+      <c r="D177">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F177" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G177" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H177" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" s="18">
+        <v>46493</v>
+      </c>
+      <c r="B178" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C178">
+        <v>192</v>
+      </c>
+      <c r="D178">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F178" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G178" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H178" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" s="18">
+        <v>46494</v>
+      </c>
+      <c r="B179" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C179">
+        <v>193</v>
+      </c>
+      <c r="D179">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F179" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G179" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H179" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" s="18">
+        <v>46495</v>
+      </c>
+      <c r="B180" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C180">
+        <v>194</v>
+      </c>
+      <c r="D180">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F180" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G180" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H180" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" s="18">
+        <v>46496</v>
+      </c>
+      <c r="B181" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C181">
+        <v>195</v>
+      </c>
+      <c r="D181">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F181" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G181" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H181" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" s="18">
+        <v>46497</v>
+      </c>
+      <c r="B182" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C182">
+        <v>196</v>
+      </c>
+      <c r="D182">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F182" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G182" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H182" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" s="18">
+        <v>46498</v>
+      </c>
+      <c r="B183" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C183">
+        <v>197</v>
+      </c>
+      <c r="D183">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F183" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G183" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H183" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" s="18">
+        <v>46499</v>
+      </c>
+      <c r="B184" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C184">
+        <v>198</v>
+      </c>
+      <c r="D184">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F184" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G184" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H184" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" s="18">
+        <v>46500</v>
+      </c>
+      <c r="B185" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C185">
+        <v>199</v>
+      </c>
+      <c r="D185">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F185" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G185" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H185" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" s="18">
+        <v>46501</v>
+      </c>
+      <c r="B186" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C186">
+        <v>200</v>
+      </c>
+      <c r="D186">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F186" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G186" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H186" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" s="18">
+        <v>46502</v>
+      </c>
+      <c r="B187" t="str">
+        <f t="shared" si="2"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C187">
+        <v>201</v>
+      </c>
+      <c r="D187">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F187" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G187" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H187" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" s="18">
+        <v>46503</v>
+      </c>
+      <c r="B188" t="str">
+        <f t="shared" si="2"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C188">
+        <v>202</v>
+      </c>
+      <c r="D188">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F188" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G188" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H188" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" s="18">
+        <v>46504</v>
+      </c>
+      <c r="B189" t="str">
+        <f t="shared" si="2"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C189">
+        <v>203</v>
+      </c>
+      <c r="D189">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F189" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G189" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H189" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" s="18">
+        <v>46505</v>
+      </c>
+      <c r="B190" t="str">
+        <f t="shared" si="2"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C190">
+        <v>204</v>
+      </c>
+      <c r="D190">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F190" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G190" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H190" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" s="18">
+        <v>46506</v>
+      </c>
+      <c r="B191" t="str">
+        <f t="shared" si="2"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C191">
+        <v>205</v>
+      </c>
+      <c r="D191">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F191" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G191" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H191" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" s="18">
+        <v>46507</v>
+      </c>
+      <c r="B192" t="str">
+        <f t="shared" si="2"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C192">
+        <v>206</v>
+      </c>
+      <c r="D192">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F192" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G192" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H192" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" s="18">
+        <v>46508</v>
+      </c>
+      <c r="B193" t="str">
+        <f t="shared" si="2"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C193">
+        <v>207</v>
+      </c>
+      <c r="D193">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F193" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G193" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H193" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" s="18">
+        <v>46509</v>
+      </c>
+      <c r="B194" t="str">
+        <f t="shared" ref="B194:B257" si="3">UPPER(TEXT(A194,"dddd"))</f>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C194">
+        <v>208</v>
+      </c>
+      <c r="D194">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F194" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G194" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H194" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" s="18">
+        <v>46510</v>
+      </c>
+      <c r="B195" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C195">
+        <v>209</v>
+      </c>
+      <c r="D195">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F195" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G195" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H195" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" s="18">
+        <v>46511</v>
+      </c>
+      <c r="B196" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C196">
+        <v>210</v>
+      </c>
+      <c r="D196">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F196" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G196" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H196" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" s="18">
+        <v>46512</v>
+      </c>
+      <c r="B197" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C197">
+        <v>211</v>
+      </c>
+      <c r="D197">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F197" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G197" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H197" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" s="18">
+        <v>46513</v>
+      </c>
+      <c r="B198" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C198">
+        <v>212</v>
+      </c>
+      <c r="D198">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F198" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G198" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H198" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" s="18">
+        <v>46514</v>
+      </c>
+      <c r="B199" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C199">
+        <v>213</v>
+      </c>
+      <c r="D199">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F199" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G199" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H199" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" s="18">
+        <v>46515</v>
+      </c>
+      <c r="B200" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C200">
+        <v>214</v>
+      </c>
+      <c r="D200">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F200" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G200" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H200" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" s="18">
+        <v>46516</v>
+      </c>
+      <c r="B201" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C201">
+        <v>215</v>
+      </c>
+      <c r="D201">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F201" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G201" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H201" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" s="18">
+        <v>46517</v>
+      </c>
+      <c r="B202" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C202">
+        <v>216</v>
+      </c>
+      <c r="D202">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F202" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G202" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H202" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" s="18">
+        <v>46518</v>
+      </c>
+      <c r="B203" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C203">
+        <v>217</v>
+      </c>
+      <c r="D203">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F203" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G203" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H203" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" s="18">
+        <v>46519</v>
+      </c>
+      <c r="B204" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C204">
+        <v>218</v>
+      </c>
+      <c r="D204">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F204" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G204" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H204" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" s="18">
+        <v>46520</v>
+      </c>
+      <c r="B205" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C205">
+        <v>219</v>
+      </c>
+      <c r="D205">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F205" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G205" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H205" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" s="18">
+        <v>46521</v>
+      </c>
+      <c r="B206" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C206">
+        <v>220</v>
+      </c>
+      <c r="D206">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F206" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G206" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H206" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" s="18">
+        <v>46522</v>
+      </c>
+      <c r="B207" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C207">
+        <v>221</v>
+      </c>
+      <c r="D207">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F207" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G207" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H207" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" s="18">
+        <v>46523</v>
+      </c>
+      <c r="B208" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C208">
+        <v>222</v>
+      </c>
+      <c r="D208">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F208" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G208" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H208" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" s="18">
+        <v>46524</v>
+      </c>
+      <c r="B209" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C209">
+        <v>223</v>
+      </c>
+      <c r="D209">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F209" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G209" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H209" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" s="18">
+        <v>46525</v>
+      </c>
+      <c r="B210" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C210">
+        <v>224</v>
+      </c>
+      <c r="D210">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F210" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G210" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H210" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" s="18">
+        <v>46526</v>
+      </c>
+      <c r="B211" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C211">
+        <v>225</v>
+      </c>
+      <c r="D211">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F211" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G211" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H211" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" s="18">
+        <v>46527</v>
+      </c>
+      <c r="B212" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C212">
+        <v>226</v>
+      </c>
+      <c r="D212">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F212" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G212" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H212" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" s="18">
+        <v>46528</v>
+      </c>
+      <c r="B213" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C213">
+        <v>227</v>
+      </c>
+      <c r="D213">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F213" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G213" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H213" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" s="18">
+        <v>46529</v>
+      </c>
+      <c r="B214" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C214">
+        <v>228</v>
+      </c>
+      <c r="D214">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F214" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G214" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H214" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" s="18">
+        <v>46530</v>
+      </c>
+      <c r="B215" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C215">
+        <v>229</v>
+      </c>
+      <c r="D215">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F215" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G215" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H215" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" s="18">
+        <v>46531</v>
+      </c>
+      <c r="B216" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C216">
+        <v>230</v>
+      </c>
+      <c r="D216">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F216" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G216" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H216" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" s="18">
+        <v>46532</v>
+      </c>
+      <c r="B217" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C217">
+        <v>231</v>
+      </c>
+      <c r="D217">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F217" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G217" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H217" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" s="18">
+        <v>46533</v>
+      </c>
+      <c r="B218" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C218">
+        <v>232</v>
+      </c>
+      <c r="D218">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F218" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G218" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H218" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" s="18">
+        <v>46534</v>
+      </c>
+      <c r="B219" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C219">
+        <v>233</v>
+      </c>
+      <c r="D219">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F219" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G219" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H219" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" s="18">
+        <v>46535</v>
+      </c>
+      <c r="B220" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C220">
+        <v>234</v>
+      </c>
+      <c r="D220">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F220" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G220" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H220" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" s="18">
+        <v>46536</v>
+      </c>
+      <c r="B221" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C221">
+        <v>235</v>
+      </c>
+      <c r="D221">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F221" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G221" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H221" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" s="18">
+        <v>46537</v>
+      </c>
+      <c r="B222" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C222">
+        <v>236</v>
+      </c>
+      <c r="D222">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F222" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G222" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H222" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" s="18">
+        <v>46538</v>
+      </c>
+      <c r="B223" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C223">
+        <v>237</v>
+      </c>
+      <c r="D223">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F223" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G223" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H223" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" s="18">
+        <v>46539</v>
+      </c>
+      <c r="B224" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C224">
+        <v>238</v>
+      </c>
+      <c r="D224">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F224" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G224" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H224" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" s="18">
+        <v>46540</v>
+      </c>
+      <c r="B225" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C225">
+        <v>239</v>
+      </c>
+      <c r="D225">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F225" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G225" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H225" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" s="18">
+        <v>46541</v>
+      </c>
+      <c r="B226" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C226">
+        <v>240</v>
+      </c>
+      <c r="D226">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F226" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G226" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H226" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" s="18">
+        <v>46542</v>
+      </c>
+      <c r="B227" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C227">
+        <v>241</v>
+      </c>
+      <c r="D227">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F227" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G227" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H227" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" s="18">
+        <v>46543</v>
+      </c>
+      <c r="B228" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C228">
+        <v>242</v>
+      </c>
+      <c r="D228">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F228" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G228" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H228" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" s="18">
+        <v>46544</v>
+      </c>
+      <c r="B229" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C229">
+        <v>243</v>
+      </c>
+      <c r="D229">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F229" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G229" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H229" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" s="18">
+        <v>46545</v>
+      </c>
+      <c r="B230" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C230">
+        <v>244</v>
+      </c>
+      <c r="D230">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F230" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G230" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H230" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" s="18">
+        <v>46546</v>
+      </c>
+      <c r="B231" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C231">
+        <v>245</v>
+      </c>
+      <c r="D231">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F231" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G231" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H231" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" s="18">
+        <v>46547</v>
+      </c>
+      <c r="B232" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C232">
+        <v>246</v>
+      </c>
+      <c r="D232">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F232" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G232" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H232" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" s="18">
+        <v>46548</v>
+      </c>
+      <c r="B233" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C233">
+        <v>247</v>
+      </c>
+      <c r="D233">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F233" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G233" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H233" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" s="18">
+        <v>46549</v>
+      </c>
+      <c r="B234" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C234">
+        <v>248</v>
+      </c>
+      <c r="D234">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F234" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G234" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H234" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" s="18">
+        <v>46550</v>
+      </c>
+      <c r="B235" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C235">
+        <v>249</v>
+      </c>
+      <c r="D235">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F235" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G235" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H235" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" s="18">
+        <v>46551</v>
+      </c>
+      <c r="B236" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C236">
+        <v>250</v>
+      </c>
+      <c r="D236">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F236" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G236" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H236" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" s="18">
+        <v>46552</v>
+      </c>
+      <c r="B237" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C237">
+        <v>251</v>
+      </c>
+      <c r="D237">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F237" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G237" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H237" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" s="18">
+        <v>46553</v>
+      </c>
+      <c r="B238" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C238">
+        <v>252</v>
+      </c>
+      <c r="D238">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F238" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G238" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H238" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" s="18">
+        <v>46554</v>
+      </c>
+      <c r="B239" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C239">
+        <v>253</v>
+      </c>
+      <c r="D239">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F239" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G239" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H239" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" s="18">
+        <v>46555</v>
+      </c>
+      <c r="B240" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C240">
+        <v>254</v>
+      </c>
+      <c r="D240">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F240" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G240" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H240" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" s="18">
+        <v>46556</v>
+      </c>
+      <c r="B241" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C241">
+        <v>255</v>
+      </c>
+      <c r="D241">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F241" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G241" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H241" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" s="18">
+        <v>46557</v>
+      </c>
+      <c r="B242" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C242">
+        <v>256</v>
+      </c>
+      <c r="D242">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F242" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G242" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H242" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" s="18">
+        <v>46558</v>
+      </c>
+      <c r="B243" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C243">
+        <v>257</v>
+      </c>
+      <c r="D243">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F243" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G243" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H243" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" s="18">
+        <v>46559</v>
+      </c>
+      <c r="B244" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C244">
+        <v>258</v>
+      </c>
+      <c r="D244">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F244" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G244" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H244" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" s="18">
+        <v>46560</v>
+      </c>
+      <c r="B245" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C245">
+        <v>259</v>
+      </c>
+      <c r="D245">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F245" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G245" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H245" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" s="18">
+        <v>46561</v>
+      </c>
+      <c r="B246" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C246">
+        <v>260</v>
+      </c>
+      <c r="D246">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F246" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G246" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H246" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" s="18">
+        <v>46562</v>
+      </c>
+      <c r="B247" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C247">
+        <v>261</v>
+      </c>
+      <c r="D247">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F247" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G247" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H247" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" s="18">
+        <v>46563</v>
+      </c>
+      <c r="B248" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C248">
+        <v>262</v>
+      </c>
+      <c r="D248">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F248" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G248" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H248" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" s="18">
+        <v>46564</v>
+      </c>
+      <c r="B249" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C249">
+        <v>263</v>
+      </c>
+      <c r="D249">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F249" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G249" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H249" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" s="18">
+        <v>46565</v>
+      </c>
+      <c r="B250" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C250">
+        <v>264</v>
+      </c>
+      <c r="D250">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F250" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G250" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H250" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" s="18">
+        <v>46566</v>
+      </c>
+      <c r="B251" t="str">
+        <f t="shared" si="3"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C251">
+        <v>265</v>
+      </c>
+      <c r="D251">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F251" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G251" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H251" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" s="18">
+        <v>46567</v>
+      </c>
+      <c r="B252" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C252">
+        <v>266</v>
+      </c>
+      <c r="D252">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F252" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G252" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H252" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" s="18">
+        <v>46568</v>
+      </c>
+      <c r="B253" t="str">
+        <f t="shared" si="3"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C253">
+        <v>267</v>
+      </c>
+      <c r="D253">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F253" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G253" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H253" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" s="18">
+        <v>46569</v>
+      </c>
+      <c r="B254" t="str">
+        <f t="shared" si="3"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C254">
+        <v>268</v>
+      </c>
+      <c r="D254">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F254" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G254" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H254" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" s="18">
+        <v>46570</v>
+      </c>
+      <c r="B255" t="str">
+        <f t="shared" si="3"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C255">
+        <v>269</v>
+      </c>
+      <c r="D255">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F255" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G255" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H255" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" s="18">
+        <v>46571</v>
+      </c>
+      <c r="B256" t="str">
+        <f t="shared" si="3"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C256">
+        <v>270</v>
+      </c>
+      <c r="D256">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F256" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G256" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H256" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" s="18">
+        <v>46572</v>
+      </c>
+      <c r="B257" t="str">
+        <f t="shared" si="3"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C257">
+        <v>271</v>
+      </c>
+      <c r="D257">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F257" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G257" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H257" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" s="18">
+        <v>46573</v>
+      </c>
+      <c r="B258" t="str">
+        <f t="shared" ref="B258:B271" si="4">UPPER(TEXT(A258,"dddd"))</f>
+        <v>LUNES</v>
+      </c>
+      <c r="C258">
+        <v>272</v>
+      </c>
+      <c r="D258">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F258" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G258" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H258" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" s="18">
+        <v>46574</v>
+      </c>
+      <c r="B259" t="str">
+        <f t="shared" si="4"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C259">
+        <v>273</v>
+      </c>
+      <c r="D259">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F259" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G259" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H259" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" s="18">
+        <v>46575</v>
+      </c>
+      <c r="B260" t="str">
+        <f t="shared" si="4"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C260">
+        <v>274</v>
+      </c>
+      <c r="D260">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F260" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G260" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H260" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" s="18">
+        <v>46576</v>
+      </c>
+      <c r="B261" t="str">
+        <f t="shared" si="4"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C261">
+        <v>275</v>
+      </c>
+      <c r="D261">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F261" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G261" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H261" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" s="18">
+        <v>46577</v>
+      </c>
+      <c r="B262" t="str">
+        <f t="shared" si="4"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C262">
+        <v>276</v>
+      </c>
+      <c r="D262">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F262" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G262" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H262" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" s="18">
+        <v>46578</v>
+      </c>
+      <c r="B263" t="str">
+        <f t="shared" si="4"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C263">
+        <v>277</v>
+      </c>
+      <c r="D263">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F263" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G263" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H263" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" s="18">
+        <v>46579</v>
+      </c>
+      <c r="B264" t="str">
+        <f t="shared" si="4"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C264">
+        <v>278</v>
+      </c>
+      <c r="D264">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F264" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G264" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H264" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" s="18">
+        <v>46580</v>
+      </c>
+      <c r="B265" t="str">
+        <f t="shared" si="4"/>
+        <v>LUNES</v>
+      </c>
+      <c r="C265">
+        <v>279</v>
+      </c>
+      <c r="D265">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F265" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G265" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H265" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" s="18">
+        <v>46581</v>
+      </c>
+      <c r="B266" t="str">
+        <f t="shared" si="4"/>
+        <v>MARTES</v>
+      </c>
+      <c r="C266">
+        <v>280</v>
+      </c>
+      <c r="D266">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F266" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G266" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H266" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" s="18">
+        <v>46582</v>
+      </c>
+      <c r="B267" t="str">
+        <f t="shared" si="4"/>
+        <v>MIÉRCOLES</v>
+      </c>
+      <c r="C267">
+        <v>281</v>
+      </c>
+      <c r="D267">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F267" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G267" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H267" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" s="18">
+        <v>46583</v>
+      </c>
+      <c r="B268" t="str">
+        <f t="shared" si="4"/>
+        <v>JUEVES</v>
+      </c>
+      <c r="C268">
+        <v>282</v>
+      </c>
+      <c r="D268">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>2</v>
+      </c>
+      <c r="F268" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G268" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H268" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" s="18">
+        <v>46584</v>
+      </c>
+      <c r="B269" t="str">
+        <f t="shared" si="4"/>
+        <v>VIERNES</v>
+      </c>
+      <c r="C269">
+        <v>283</v>
+      </c>
+      <c r="D269">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>1</v>
+      </c>
+      <c r="F269" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G269" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H269" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
+      <c r="A270" s="18">
+        <v>46585</v>
+      </c>
+      <c r="B270" t="str">
+        <f t="shared" si="4"/>
+        <v>SÁBADO</v>
+      </c>
+      <c r="C270">
+        <v>284</v>
+      </c>
+      <c r="D270">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F270" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G270" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H270" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" s="18">
+        <v>46586</v>
+      </c>
+      <c r="B271" t="str">
+        <f t="shared" si="4"/>
+        <v>DOMINGO</v>
+      </c>
+      <c r="C271">
+        <v>285</v>
+      </c>
+      <c r="D271">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="F271" s="17">
+        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
+        <v>0</v>
+      </c>
+      <c r="G271" s="17">
+        <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
+        <v>0</v>
+      </c>
+      <c r="H271" s="17">
+        <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
+        <v>0</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{9A17B10D-5904-45FC-8455-E0B87D4F73D5}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3A15D755-8C74-4EB2-9D54-98BB2B1DDC10}">
+          <x14:formula1>
+            <xm:f>Etapas!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E271</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF69EA8-A442-49C1-970D-30A5A570B9C5}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5965AE26-C0EC-4F4E-BC80-7109B017A151}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="17">
+        <v>0.02</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+      <c r="G2" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H2" s="16">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="17">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C3">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>70</v>
+      </c>
+      <c r="G3" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H3" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="17">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>90</v>
+      </c>
+      <c r="G4" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H4" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="17">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
+      </c>
+      <c r="F5">
+        <v>90</v>
+      </c>
+      <c r="G5" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H5" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="I5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="17">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="C6">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>90</v>
+      </c>
+      <c r="G6" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H6" s="16">
+        <v>0.7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="17">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26C9A4A3-56C8-43B7-99C8-64F48BAC84CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5987E5C0-17FC-4BAC-8FFC-ED8DA8BB1910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diario Completo Leo" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="86">
   <si>
     <t>Fecha</t>
   </si>
@@ -153,6 +153,12 @@
     <t>Respeto mi filtro y cuido mi capital: esperar también es operar con inteligencia.</t>
   </si>
   <si>
+    <t>PA 65, No se ingresa por reglas</t>
+  </si>
+  <si>
+    <t>Hoy el precio no cumplió las reglas (PA 65) y no entré. Lo que sí hice fue ajustar con disciplina y proteger el capital en el retroceso. Cerré con una pérdida de -0,28%, y lo acepto como parte del proceso.</t>
+  </si>
+  <si>
     <t>Dia Semana</t>
   </si>
   <si>
@@ -213,6 +219,18 @@
     <t>08:30 Core PCE Price Index m/m, Prelim GDP q/q</t>
   </si>
   <si>
+    <t>Aceleración</t>
+  </si>
+  <si>
+    <t>Pro</t>
+  </si>
+  <si>
+    <t>Pro 500</t>
+  </si>
+  <si>
+    <t>Pro M</t>
+  </si>
+  <si>
     <t>DIA DE LA SEMANA</t>
   </si>
   <si>
@@ -270,25 +288,13 @@
     <t>$1,000 → $2,000</t>
   </si>
   <si>
-    <t>Aceleración</t>
-  </si>
-  <si>
     <t>$2,000 → $5,000</t>
-  </si>
-  <si>
-    <t>Pro</t>
   </si>
   <si>
     <t>$5,000 → $10,000</t>
   </si>
   <si>
-    <t>Pro 500</t>
-  </si>
-  <si>
     <t>$10,000 → $20,000</t>
-  </si>
-  <si>
-    <t>Pro M</t>
   </si>
   <si>
     <t>$20,000 → $1,000,000</t>
@@ -594,8 +600,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P9" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:P9" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P10" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
+  <autoFilter ref="A1:P10" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
@@ -979,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
@@ -1400,6 +1406,54 @@
         <v>36</v>
       </c>
     </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="10">
+        <f>K9+L9</f>
+        <v>520.04</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10">
+        <v>-1.41</v>
+      </c>
+      <c r="H10" s="10">
+        <v>-0.06</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>518.57000000000005</v>
+      </c>
+      <c r="L10" s="10"/>
+      <c r="M10" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>-0.28267056380278444</v>
+      </c>
+      <c r="N10" s="12">
+        <f>Tabla13[[#This Row],[% día]]</f>
+        <v>-0.28267056380278444</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
     <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
@@ -1417,7 +1471,7 @@
           <x14:formula1>
             <xm:f>Etapas!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B9</xm:sqref>
+          <xm:sqref>B2:B10</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1446,31 +1500,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1712,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1749,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1922,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2009,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2027,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2046,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F18" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2080,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2114,7 +2168,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F20" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2148,7 +2202,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F21" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2166,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2185,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F22" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2203,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2222,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F23" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2256,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F24" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2274,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2293,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F25" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2327,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F26" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2361,7 +2415,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F27" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2395,7 +2449,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F28" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2413,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2432,7 +2486,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F29" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2450,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2469,7 +2523,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F30" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2503,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F31" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2537,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F32" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2571,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2605,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2639,7 +2693,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F35" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2673,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F36" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2691,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2710,7 +2764,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F37" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2728,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2747,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F38" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2781,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F39" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2815,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F40" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2849,7 +2903,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F41" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2883,7 +2937,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F42" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2917,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F43" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2951,7 +3005,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F44" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2985,7 +3039,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F45" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3019,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F46" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3053,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F47" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3087,7 +3141,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F48" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3121,7 +3175,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F49" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3155,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F50" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3189,7 +3243,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F51" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3223,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F52" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3257,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F53" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3291,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F54" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3325,7 +3379,7 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F55" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3359,7 +3413,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F56" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3393,7 +3447,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F57" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3427,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F58" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3461,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F59" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3495,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F60" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3529,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F61" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3563,7 +3617,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F62" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3597,7 +3651,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F63" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3631,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F64" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3665,7 +3719,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F65" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3699,7 +3753,7 @@
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F66" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3733,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F67" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3767,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F68" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3801,7 +3855,7 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F69" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3835,7 +3889,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F70" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3869,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F71" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3903,7 +3957,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F72" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3936,17 +3990,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E73" t="s">
+        <v>51</v>
+      </c>
       <c r="F73" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G73" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="H73" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3967,9 +4024,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E74" t="s">
+        <v>51</v>
+      </c>
       <c r="F74" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G74" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -3998,9 +4058,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E75" t="s">
+        <v>51</v>
+      </c>
       <c r="F75" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G75" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4029,17 +4092,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E76" t="s">
+        <v>51</v>
+      </c>
       <c r="F76" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G76" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H76" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -4060,17 +4126,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E77" t="s">
+        <v>59</v>
+      </c>
       <c r="F77" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G77" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H77" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -4091,17 +4160,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E78" t="s">
+        <v>59</v>
+      </c>
       <c r="F78" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G78" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H78" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -4122,17 +4194,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E79" t="s">
+        <v>59</v>
+      </c>
       <c r="F79" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G79" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H79" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -4153,17 +4228,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E80" t="s">
+        <v>59</v>
+      </c>
       <c r="F80" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G80" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H80" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4184,9 +4262,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E81" t="s">
+        <v>59</v>
+      </c>
       <c r="F81" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G81" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4215,9 +4296,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E82" t="s">
+        <v>59</v>
+      </c>
       <c r="F82" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G82" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4246,17 +4330,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E83" t="s">
+        <v>59</v>
+      </c>
       <c r="F83" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G83" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H83" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4277,17 +4364,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E84" t="s">
+        <v>59</v>
+      </c>
       <c r="F84" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G84" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H84" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4308,17 +4398,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E85" t="s">
+        <v>59</v>
+      </c>
       <c r="F85" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G85" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H85" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -4339,17 +4432,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E86" t="s">
+        <v>59</v>
+      </c>
       <c r="F86" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G86" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H86" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -4370,17 +4466,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E87" t="s">
+        <v>59</v>
+      </c>
       <c r="F87" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G87" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H87" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4401,9 +4500,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E88" t="s">
+        <v>59</v>
+      </c>
       <c r="F88" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G88" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4432,9 +4534,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E89" t="s">
+        <v>59</v>
+      </c>
       <c r="F89" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G89" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4463,17 +4568,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E90" t="s">
+        <v>59</v>
+      </c>
       <c r="F90" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G90" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H90" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -4494,17 +4602,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E91" t="s">
+        <v>59</v>
+      </c>
       <c r="F91" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G91" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H91" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -4525,17 +4636,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E92" t="s">
+        <v>59</v>
+      </c>
       <c r="F92" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G92" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H92" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4556,17 +4670,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E93" t="s">
+        <v>59</v>
+      </c>
       <c r="F93" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G93" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H93" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -4587,17 +4704,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E94" t="s">
+        <v>59</v>
+      </c>
       <c r="F94" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G94" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H94" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -4618,9 +4738,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E95" t="s">
+        <v>59</v>
+      </c>
       <c r="F95" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G95" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4649,9 +4772,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E96" t="s">
+        <v>59</v>
+      </c>
       <c r="F96" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G96" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4680,17 +4806,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E97" t="s">
+        <v>59</v>
+      </c>
       <c r="F97" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G97" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H97" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4711,17 +4840,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E98" t="s">
+        <v>59</v>
+      </c>
       <c r="F98" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G98" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H98" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -4742,17 +4874,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E99" t="s">
+        <v>59</v>
+      </c>
       <c r="F99" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G99" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H99" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -4773,17 +4908,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E100" t="s">
+        <v>59</v>
+      </c>
       <c r="F100" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G100" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H100" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -4804,17 +4942,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E101" t="s">
+        <v>59</v>
+      </c>
       <c r="F101" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G101" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H101" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -4835,9 +4976,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E102" t="s">
+        <v>59</v>
+      </c>
       <c r="F102" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G102" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4866,9 +5010,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E103" t="s">
+        <v>59</v>
+      </c>
       <c r="F103" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G103" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -4897,17 +5044,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E104" t="s">
+        <v>59</v>
+      </c>
       <c r="F104" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G104" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H104" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -4928,17 +5078,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E105" t="s">
+        <v>59</v>
+      </c>
       <c r="F105" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G105" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H105" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -4959,17 +5112,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E106" t="s">
+        <v>59</v>
+      </c>
       <c r="F106" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G106" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H106" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -4990,17 +5146,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E107" t="s">
+        <v>59</v>
+      </c>
       <c r="F107" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G107" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H107" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -5021,17 +5180,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E108" t="s">
+        <v>59</v>
+      </c>
       <c r="F108" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G108" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H108" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -5052,9 +5214,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E109" t="s">
+        <v>59</v>
+      </c>
       <c r="F109" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G109" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5083,9 +5248,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E110" t="s">
+        <v>59</v>
+      </c>
       <c r="F110" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G110" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5114,17 +5282,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E111" t="s">
+        <v>59</v>
+      </c>
       <c r="F111" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G111" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H111" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -5145,17 +5316,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E112" t="s">
+        <v>59</v>
+      </c>
       <c r="F112" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G112" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H112" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5176,17 +5350,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E113" t="s">
+        <v>59</v>
+      </c>
       <c r="F113" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G113" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H113" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I113">
         <v>0</v>
@@ -5207,17 +5384,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E114" t="s">
+        <v>59</v>
+      </c>
       <c r="F114" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G114" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H114" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -5238,17 +5418,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E115" t="s">
+        <v>59</v>
+      </c>
       <c r="F115" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G115" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H115" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -5269,9 +5452,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E116" t="s">
+        <v>59</v>
+      </c>
       <c r="F116" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G116" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5300,9 +5486,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E117" t="s">
+        <v>59</v>
+      </c>
       <c r="F117" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G117" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5331,17 +5520,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E118" t="s">
+        <v>59</v>
+      </c>
       <c r="F118" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G118" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H118" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -5362,17 +5554,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E119" t="s">
+        <v>59</v>
+      </c>
       <c r="F119" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G119" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H119" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -5393,17 +5588,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E120" t="s">
+        <v>59</v>
+      </c>
       <c r="F120" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G120" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H120" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -5424,17 +5622,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E121" t="s">
+        <v>59</v>
+      </c>
       <c r="F121" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G121" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H121" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -5455,17 +5656,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E122" t="s">
+        <v>59</v>
+      </c>
       <c r="F122" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G122" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H122" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -5486,9 +5690,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E123" t="s">
+        <v>59</v>
+      </c>
       <c r="F123" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G123" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5517,9 +5724,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E124" t="s">
+        <v>59</v>
+      </c>
       <c r="F124" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G124" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5548,17 +5758,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E125" t="s">
+        <v>59</v>
+      </c>
       <c r="F125" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G125" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H125" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -5579,17 +5792,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E126" t="s">
+        <v>59</v>
+      </c>
       <c r="F126" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G126" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H126" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -5610,17 +5826,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E127" t="s">
+        <v>59</v>
+      </c>
       <c r="F127" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G127" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H127" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -5641,17 +5860,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E128" t="s">
+        <v>59</v>
+      </c>
       <c r="F128" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G128" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H128" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -5672,17 +5894,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E129" t="s">
+        <v>59</v>
+      </c>
       <c r="F129" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G129" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H129" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -5703,9 +5928,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E130" t="s">
+        <v>59</v>
+      </c>
       <c r="F130" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G130" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5734,9 +5962,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E131" t="s">
+        <v>59</v>
+      </c>
       <c r="F131" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G131" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5765,17 +5996,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E132" t="s">
+        <v>59</v>
+      </c>
       <c r="F132" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G132" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H132" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I132">
         <v>0</v>
@@ -5796,17 +6030,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E133" t="s">
+        <v>59</v>
+      </c>
       <c r="F133" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G133" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H133" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I133">
         <v>0</v>
@@ -5827,17 +6064,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E134" t="s">
+        <v>59</v>
+      </c>
       <c r="F134" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G134" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H134" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -5858,17 +6098,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E135" t="s">
+        <v>59</v>
+      </c>
       <c r="F135" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G135" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H135" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -5889,17 +6132,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E136" t="s">
+        <v>59</v>
+      </c>
       <c r="F136" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G136" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H136" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -5920,9 +6166,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E137" t="s">
+        <v>60</v>
+      </c>
       <c r="F137" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G137" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5951,9 +6200,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E138" t="s">
+        <v>60</v>
+      </c>
       <c r="F138" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G138" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -5982,17 +6234,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E139" t="s">
+        <v>60</v>
+      </c>
       <c r="F139" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G139" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H139" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -6013,17 +6268,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E140" t="s">
+        <v>60</v>
+      </c>
       <c r="F140" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G140" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H140" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I140">
         <v>0</v>
@@ -6044,17 +6302,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E141" t="s">
+        <v>60</v>
+      </c>
       <c r="F141" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G141" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H141" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I141">
         <v>0</v>
@@ -6075,17 +6336,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E142" t="s">
+        <v>60</v>
+      </c>
       <c r="F142" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G142" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H142" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -6106,17 +6370,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E143" t="s">
+        <v>60</v>
+      </c>
       <c r="F143" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G143" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H143" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -6137,9 +6404,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E144" t="s">
+        <v>60</v>
+      </c>
       <c r="F144" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G144" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6168,9 +6438,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E145" t="s">
+        <v>60</v>
+      </c>
       <c r="F145" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G145" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6199,17 +6472,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E146" t="s">
+        <v>60</v>
+      </c>
       <c r="F146" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G146" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H146" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -6230,17 +6506,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E147" t="s">
+        <v>60</v>
+      </c>
       <c r="F147" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G147" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H147" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -6261,17 +6540,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E148" t="s">
+        <v>60</v>
+      </c>
       <c r="F148" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G148" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H148" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I148">
         <v>0</v>
@@ -6292,17 +6574,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E149" t="s">
+        <v>60</v>
+      </c>
       <c r="F149" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G149" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H149" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -6323,17 +6608,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E150" t="s">
+        <v>60</v>
+      </c>
       <c r="F150" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G150" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H150" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -6354,9 +6642,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E151" t="s">
+        <v>60</v>
+      </c>
       <c r="F151" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G151" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6385,9 +6676,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E152" t="s">
+        <v>60</v>
+      </c>
       <c r="F152" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G152" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6416,17 +6710,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E153" t="s">
+        <v>60</v>
+      </c>
       <c r="F153" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G153" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H153" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -6447,17 +6744,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E154" t="s">
+        <v>60</v>
+      </c>
       <c r="F154" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G154" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H154" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -6478,17 +6778,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E155" t="s">
+        <v>60</v>
+      </c>
       <c r="F155" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G155" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H155" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I155">
         <v>0</v>
@@ -6509,17 +6812,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E156" t="s">
+        <v>60</v>
+      </c>
       <c r="F156" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G156" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H156" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -6540,17 +6846,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E157" t="s">
+        <v>60</v>
+      </c>
       <c r="F157" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G157" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H157" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -6571,9 +6880,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E158" t="s">
+        <v>60</v>
+      </c>
       <c r="F158" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G158" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6602,9 +6914,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E159" t="s">
+        <v>60</v>
+      </c>
       <c r="F159" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G159" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6633,17 +6948,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E160" t="s">
+        <v>60</v>
+      </c>
       <c r="F160" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G160" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H160" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I160">
         <v>0</v>
@@ -6664,17 +6982,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E161" t="s">
+        <v>60</v>
+      </c>
       <c r="F161" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G161" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H161" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I161">
         <v>0</v>
@@ -6695,17 +7016,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E162" t="s">
+        <v>60</v>
+      </c>
       <c r="F162" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G162" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H162" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -6726,17 +7050,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E163" t="s">
+        <v>60</v>
+      </c>
       <c r="F163" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G163" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H163" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I163">
         <v>0</v>
@@ -6757,17 +7084,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E164" t="s">
+        <v>60</v>
+      </c>
       <c r="F164" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G164" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H164" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I164">
         <v>0</v>
@@ -6788,9 +7118,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E165" t="s">
+        <v>60</v>
+      </c>
       <c r="F165" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G165" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6819,9 +7152,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E166" t="s">
+        <v>60</v>
+      </c>
       <c r="F166" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G166" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -6850,17 +7186,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E167" t="s">
+        <v>60</v>
+      </c>
       <c r="F167" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G167" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H167" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -6881,17 +7220,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E168" t="s">
+        <v>60</v>
+      </c>
       <c r="F168" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G168" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H168" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I168">
         <v>0</v>
@@ -6912,17 +7254,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E169" t="s">
+        <v>60</v>
+      </c>
       <c r="F169" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G169" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H169" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I169">
         <v>0</v>
@@ -6943,17 +7288,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E170" t="s">
+        <v>60</v>
+      </c>
       <c r="F170" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G170" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H170" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -6974,17 +7322,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E171" t="s">
+        <v>60</v>
+      </c>
       <c r="F171" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G171" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H171" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -7005,9 +7356,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E172" t="s">
+        <v>60</v>
+      </c>
       <c r="F172" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G172" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7036,9 +7390,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E173" t="s">
+        <v>60</v>
+      </c>
       <c r="F173" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G173" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7067,17 +7424,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E174" t="s">
+        <v>60</v>
+      </c>
       <c r="F174" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G174" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H174" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -7098,17 +7458,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E175" t="s">
+        <v>60</v>
+      </c>
       <c r="F175" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G175" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H175" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -7129,17 +7492,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E176" t="s">
+        <v>60</v>
+      </c>
       <c r="F176" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G176" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H176" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -7160,17 +7526,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E177" t="s">
+        <v>60</v>
+      </c>
       <c r="F177" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G177" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H177" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -7191,17 +7560,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E178" t="s">
+        <v>60</v>
+      </c>
       <c r="F178" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G178" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H178" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -7222,9 +7594,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E179" t="s">
+        <v>60</v>
+      </c>
       <c r="F179" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G179" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7253,9 +7628,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E180" t="s">
+        <v>60</v>
+      </c>
       <c r="F180" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G180" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7284,17 +7662,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E181" t="s">
+        <v>60</v>
+      </c>
       <c r="F181" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G181" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H181" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -7315,17 +7696,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E182" t="s">
+        <v>60</v>
+      </c>
       <c r="F182" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G182" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H182" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I182">
         <v>0</v>
@@ -7346,17 +7730,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E183" t="s">
+        <v>60</v>
+      </c>
       <c r="F183" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G183" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H183" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I183">
         <v>0</v>
@@ -7377,17 +7764,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E184" t="s">
+        <v>60</v>
+      </c>
       <c r="F184" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G184" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H184" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -7408,17 +7798,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E185" t="s">
+        <v>60</v>
+      </c>
       <c r="F185" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G185" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H185" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -7439,9 +7832,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E186" t="s">
+        <v>60</v>
+      </c>
       <c r="F186" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G186" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7470,9 +7866,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E187" t="s">
+        <v>60</v>
+      </c>
       <c r="F187" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G187" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7501,17 +7900,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E188" t="s">
+        <v>60</v>
+      </c>
       <c r="F188" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G188" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H188" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I188">
         <v>0</v>
@@ -7532,17 +7934,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E189" t="s">
+        <v>60</v>
+      </c>
       <c r="F189" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G189" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H189" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I189">
         <v>0</v>
@@ -7563,17 +7968,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E190" t="s">
+        <v>60</v>
+      </c>
       <c r="F190" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G190" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H190" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I190">
         <v>0</v>
@@ -7594,17 +8002,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E191" t="s">
+        <v>60</v>
+      </c>
       <c r="F191" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G191" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H191" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I191">
         <v>0</v>
@@ -7625,17 +8036,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E192" t="s">
+        <v>60</v>
+      </c>
       <c r="F192" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G192" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H192" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I192">
         <v>0</v>
@@ -7656,9 +8070,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E193" t="s">
+        <v>60</v>
+      </c>
       <c r="F193" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G193" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7687,9 +8104,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E194" t="s">
+        <v>60</v>
+      </c>
       <c r="F194" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G194" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7718,17 +8138,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E195" t="s">
+        <v>60</v>
+      </c>
       <c r="F195" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G195" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H195" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I195">
         <v>0</v>
@@ -7749,17 +8172,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E196" t="s">
+        <v>60</v>
+      </c>
       <c r="F196" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G196" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H196" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I196">
         <v>0</v>
@@ -7780,17 +8206,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E197" t="s">
+        <v>61</v>
+      </c>
       <c r="F197" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G197" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H197" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I197">
         <v>0</v>
@@ -7811,17 +8240,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E198" t="s">
+        <v>61</v>
+      </c>
       <c r="F198" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G198" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H198" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I198">
         <v>0</v>
@@ -7842,17 +8274,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E199" t="s">
+        <v>61</v>
+      </c>
       <c r="F199" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G199" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H199" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -7873,9 +8308,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E200" t="s">
+        <v>61</v>
+      </c>
       <c r="F200" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G200" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7904,9 +8342,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E201" t="s">
+        <v>61</v>
+      </c>
       <c r="F201" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G201" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -7935,17 +8376,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E202" t="s">
+        <v>61</v>
+      </c>
       <c r="F202" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G202" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H202" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I202">
         <v>0</v>
@@ -7966,17 +8410,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E203" t="s">
+        <v>61</v>
+      </c>
       <c r="F203" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G203" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H203" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I203">
         <v>0</v>
@@ -7997,17 +8444,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E204" t="s">
+        <v>61</v>
+      </c>
       <c r="F204" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G204" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H204" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I204">
         <v>0</v>
@@ -8028,17 +8478,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E205" t="s">
+        <v>61</v>
+      </c>
       <c r="F205" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G205" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H205" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I205">
         <v>0</v>
@@ -8059,17 +8512,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E206" t="s">
+        <v>61</v>
+      </c>
       <c r="F206" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G206" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H206" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -8090,9 +8546,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E207" t="s">
+        <v>61</v>
+      </c>
       <c r="F207" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G207" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8121,9 +8580,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E208" t="s">
+        <v>61</v>
+      </c>
       <c r="F208" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G208" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8152,17 +8614,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E209" t="s">
+        <v>61</v>
+      </c>
       <c r="F209" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G209" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H209" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I209">
         <v>0</v>
@@ -8183,17 +8648,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E210" t="s">
+        <v>61</v>
+      </c>
       <c r="F210" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G210" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H210" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I210">
         <v>0</v>
@@ -8214,17 +8682,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E211" t="s">
+        <v>61</v>
+      </c>
       <c r="F211" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G211" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H211" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I211">
         <v>0</v>
@@ -8245,17 +8716,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E212" t="s">
+        <v>61</v>
+      </c>
       <c r="F212" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G212" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H212" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I212">
         <v>0</v>
@@ -8276,17 +8750,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E213" t="s">
+        <v>61</v>
+      </c>
       <c r="F213" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G213" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H213" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I213">
         <v>0</v>
@@ -8307,9 +8784,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E214" t="s">
+        <v>61</v>
+      </c>
       <c r="F214" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G214" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8338,9 +8818,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E215" t="s">
+        <v>61</v>
+      </c>
       <c r="F215" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G215" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8369,17 +8852,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E216" t="s">
+        <v>61</v>
+      </c>
       <c r="F216" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G216" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H216" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I216">
         <v>0</v>
@@ -8400,17 +8886,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E217" t="s">
+        <v>61</v>
+      </c>
       <c r="F217" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G217" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H217" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I217">
         <v>0</v>
@@ -8431,17 +8920,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E218" t="s">
+        <v>61</v>
+      </c>
       <c r="F218" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G218" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H218" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I218">
         <v>0</v>
@@ -8462,17 +8954,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E219" t="s">
+        <v>61</v>
+      </c>
       <c r="F219" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G219" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H219" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I219">
         <v>0</v>
@@ -8493,17 +8988,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E220" t="s">
+        <v>61</v>
+      </c>
       <c r="F220" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G220" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H220" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I220">
         <v>0</v>
@@ -8524,9 +9022,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E221" t="s">
+        <v>61</v>
+      </c>
       <c r="F221" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G221" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8555,9 +9056,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E222" t="s">
+        <v>61</v>
+      </c>
       <c r="F222" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G222" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8586,17 +9090,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E223" t="s">
+        <v>61</v>
+      </c>
       <c r="F223" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G223" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H223" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I223">
         <v>0</v>
@@ -8617,17 +9124,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E224" t="s">
+        <v>61</v>
+      </c>
       <c r="F224" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G224" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H224" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I224">
         <v>0</v>
@@ -8648,17 +9158,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E225" t="s">
+        <v>61</v>
+      </c>
       <c r="F225" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G225" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H225" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I225">
         <v>0</v>
@@ -8679,17 +9192,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E226" t="s">
+        <v>61</v>
+      </c>
       <c r="F226" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G226" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H226" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I226">
         <v>0</v>
@@ -8710,17 +9226,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E227" t="s">
+        <v>61</v>
+      </c>
       <c r="F227" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G227" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H227" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I227">
         <v>0</v>
@@ -8741,9 +9260,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E228" t="s">
+        <v>61</v>
+      </c>
       <c r="F228" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G228" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8772,9 +9294,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E229" t="s">
+        <v>61</v>
+      </c>
       <c r="F229" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G229" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8803,17 +9328,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E230" t="s">
+        <v>61</v>
+      </c>
       <c r="F230" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G230" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H230" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I230">
         <v>0</v>
@@ -8834,17 +9362,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E231" t="s">
+        <v>61</v>
+      </c>
       <c r="F231" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G231" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H231" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I231">
         <v>0</v>
@@ -8865,17 +9396,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E232" t="s">
+        <v>61</v>
+      </c>
       <c r="F232" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G232" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H232" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I232">
         <v>0</v>
@@ -8896,17 +9430,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E233" t="s">
+        <v>61</v>
+      </c>
       <c r="F233" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G233" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H233" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I233">
         <v>0</v>
@@ -8927,17 +9464,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E234" t="s">
+        <v>61</v>
+      </c>
       <c r="F234" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G234" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H234" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I234">
         <v>0</v>
@@ -8958,9 +9498,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E235" t="s">
+        <v>61</v>
+      </c>
       <c r="F235" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G235" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -8989,9 +9532,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E236" t="s">
+        <v>61</v>
+      </c>
       <c r="F236" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G236" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9020,17 +9566,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E237" t="s">
+        <v>61</v>
+      </c>
       <c r="F237" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G237" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H237" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I237">
         <v>0</v>
@@ -9051,17 +9600,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E238" t="s">
+        <v>61</v>
+      </c>
       <c r="F238" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G238" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H238" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I238">
         <v>0</v>
@@ -9082,17 +9634,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E239" t="s">
+        <v>61</v>
+      </c>
       <c r="F239" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G239" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H239" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I239">
         <v>0</v>
@@ -9113,17 +9668,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E240" t="s">
+        <v>61</v>
+      </c>
       <c r="F240" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G240" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H240" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I240">
         <v>0</v>
@@ -9144,17 +9702,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E241" t="s">
+        <v>61</v>
+      </c>
       <c r="F241" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G241" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H241" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I241">
         <v>0</v>
@@ -9175,9 +9736,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E242" t="s">
+        <v>61</v>
+      </c>
       <c r="F242" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G242" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9206,9 +9770,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E243" t="s">
+        <v>61</v>
+      </c>
       <c r="F243" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G243" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9237,17 +9804,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E244" t="s">
+        <v>61</v>
+      </c>
       <c r="F244" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G244" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H244" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I244">
         <v>0</v>
@@ -9268,17 +9838,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E245" t="s">
+        <v>61</v>
+      </c>
       <c r="F245" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G245" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H245" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I245">
         <v>0</v>
@@ -9299,17 +9872,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E246" t="s">
+        <v>61</v>
+      </c>
       <c r="F246" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G246" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H246" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I246">
         <v>0</v>
@@ -9330,17 +9906,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E247" t="s">
+        <v>61</v>
+      </c>
       <c r="F247" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G247" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H247" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I247">
         <v>0</v>
@@ -9361,17 +9940,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E248" t="s">
+        <v>61</v>
+      </c>
       <c r="F248" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G248" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H248" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I248">
         <v>0</v>
@@ -9392,9 +9974,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E249" t="s">
+        <v>61</v>
+      </c>
       <c r="F249" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G249" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9423,9 +10008,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E250" t="s">
+        <v>61</v>
+      </c>
       <c r="F250" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G250" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9454,17 +10042,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E251" t="s">
+        <v>61</v>
+      </c>
       <c r="F251" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G251" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H251" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I251">
         <v>0</v>
@@ -9485,17 +10076,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E252" t="s">
+        <v>61</v>
+      </c>
       <c r="F252" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G252" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H252" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I252">
         <v>0</v>
@@ -9516,17 +10110,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E253" t="s">
+        <v>61</v>
+      </c>
       <c r="F253" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G253" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H253" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I253">
         <v>0</v>
@@ -9547,17 +10144,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E254" t="s">
+        <v>61</v>
+      </c>
       <c r="F254" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G254" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H254" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I254">
         <v>0</v>
@@ -9578,17 +10178,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E255" t="s">
+        <v>61</v>
+      </c>
       <c r="F255" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G255" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H255" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -9609,9 +10212,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E256" t="s">
+        <v>61</v>
+      </c>
       <c r="F256" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G256" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9640,9 +10246,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E257" t="s">
+        <v>62</v>
+      </c>
       <c r="F257" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G257" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9671,17 +10280,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E258" t="s">
+        <v>62</v>
+      </c>
       <c r="F258" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G258" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H258" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I258">
         <v>0</v>
@@ -9702,17 +10314,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E259" t="s">
+        <v>62</v>
+      </c>
       <c r="F259" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G259" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H259" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I259">
         <v>0</v>
@@ -9733,17 +10348,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E260" t="s">
+        <v>62</v>
+      </c>
       <c r="F260" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G260" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H260" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I260">
         <v>0</v>
@@ -9764,17 +10382,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E261" t="s">
+        <v>62</v>
+      </c>
       <c r="F261" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G261" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H261" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I261">
         <v>0</v>
@@ -9795,17 +10416,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E262" t="s">
+        <v>62</v>
+      </c>
       <c r="F262" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G262" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H262" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I262">
         <v>0</v>
@@ -9826,9 +10450,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E263" t="s">
+        <v>62</v>
+      </c>
       <c r="F263" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G263" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9857,9 +10484,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E264" t="s">
+        <v>62</v>
+      </c>
       <c r="F264" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G264" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -9888,17 +10518,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E265" t="s">
+        <v>62</v>
+      </c>
       <c r="F265" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G265" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H265" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I265">
         <v>0</v>
@@ -9919,17 +10552,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E266" t="s">
+        <v>62</v>
+      </c>
       <c r="F266" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G266" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H266" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I266">
         <v>0</v>
@@ -9950,17 +10586,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E267" t="s">
+        <v>62</v>
+      </c>
       <c r="F267" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G267" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H267" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I267">
         <v>0</v>
@@ -9981,17 +10620,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>2</v>
       </c>
+      <c r="E268" t="s">
+        <v>62</v>
+      </c>
       <c r="F268" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G268" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="H268" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="I268">
         <v>0</v>
@@ -10012,17 +10654,20 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>1</v>
       </c>
+      <c r="E269" t="s">
+        <v>62</v>
+      </c>
       <c r="F269" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G269" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="H269" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="I269">
         <v>0</v>
@@ -10043,9 +10688,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E270" t="s">
+        <v>62</v>
+      </c>
       <c r="F270" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G270" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -10074,9 +10722,12 @@
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
         <v>0</v>
       </c>
+      <c r="E271" t="s">
+        <v>62</v>
+      </c>
       <c r="F271" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
-        <v>0</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="G271" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
@@ -10123,15 +10774,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -10139,7 +10790,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10147,7 +10798,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -10155,7 +10806,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10163,7 +10814,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -10171,7 +10822,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10179,7 +10830,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10210,31 +10861,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -10263,12 +10914,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="17">
         <v>5.0000000000000001E-3</v>
@@ -10292,12 +10943,12 @@
         <v>0.4</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B4" s="17">
         <v>3.5000000000000001E-3</v>
@@ -10321,12 +10972,12 @@
         <v>0.5</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B5" s="17">
         <v>3.5000000000000001E-3</v>
@@ -10350,12 +11001,12 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B6" s="17">
         <v>3.5000000000000001E-3</v>
@@ -10379,12 +11030,12 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B7" s="17">
         <v>3.5000000000000001E-3</v>
@@ -10408,7 +11059,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5987E5C0-17FC-4BAC-8FFC-ED8DA8BB1910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DD039AD-051E-4A3F-ADB2-4695708B15A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Diario Completo Leo" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="88">
   <si>
     <t>Fecha</t>
   </si>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t>Hoy el precio no cumplió las reglas (PA 65) y no entré. Lo que sí hice fue ajustar con disciplina y proteger el capital en el retroceso. Cerré con una pérdida de -0,28%, y lo acepto como parte del proceso.</t>
+  </si>
+  <si>
+    <t>PA 72, No se ingresa por reglas</t>
+  </si>
+  <si>
+    <t>Mi paciencia es mi ventaja: actúo solo cuando mis reglas lo confirman.</t>
   </si>
   <si>
     <t>Dia Semana</t>
@@ -600,8 +606,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P10" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:P10" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P11" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
+  <autoFilter ref="A1:P11" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
@@ -621,7 +627,7 @@
       <calculatedColumnFormula>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{37FC7929-CC89-4264-919C-26D755C48B12}" name="% Acumulado" dataDxfId="10">
-      <calculatedColumnFormula>Tabla13[[#This Row],[% día]]</calculatedColumnFormula>
+      <calculatedColumnFormula>(K2-$C$2)/($C$2)*100</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{258B4FD8-869C-4D06-AEC0-881ADBF62A78}" name="Observaciones" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{0A710856-9F8D-4D22-98FF-8507E77747D3}" name="Concepto" dataDxfId="8"/>
@@ -985,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
@@ -1085,7 +1091,8 @@
         <v>0.81919926156686274</v>
       </c>
       <c r="N2" s="12">
-        <v>0.82</v>
+        <f t="shared" ref="N2:N11" si="0">(K2-$C$2)/($C$2)*100</f>
+        <v>0.81919926156686107</v>
       </c>
       <c r="O2" s="11" t="s">
         <v>19</v>
@@ -1128,8 +1135,8 @@
         <v>0</v>
       </c>
       <c r="N3" s="12">
-        <f>Tabla13[[#This Row],[% día]]+N2</f>
-        <v>0.82</v>
+        <f t="shared" si="0"/>
+        <v>0.81919926156686107</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>22</v>
@@ -1170,8 +1177,8 @@
         <v>0</v>
       </c>
       <c r="N4" s="12">
-        <f>Tabla13[[#This Row],[% día]]+N3</f>
-        <v>0.82</v>
+        <f t="shared" si="0"/>
+        <v>0.81919926156686107</v>
       </c>
       <c r="O4" s="11" t="s">
         <v>24</v>
@@ -1212,8 +1219,8 @@
         <v>0</v>
       </c>
       <c r="N5" s="12">
-        <f>Tabla13[[#This Row],[% día]]+N4</f>
-        <v>0.82</v>
+        <f t="shared" si="0"/>
+        <v>0.81919926156686107</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>26</v>
@@ -1254,8 +1261,8 @@
         <v>0</v>
       </c>
       <c r="N6" s="12">
-        <f>Tabla13[[#This Row],[% día]]+N5</f>
-        <v>0.82</v>
+        <f t="shared" si="0"/>
+        <v>0.81919926156686107</v>
       </c>
       <c r="O6" s="11" t="s">
         <v>28</v>
@@ -1302,8 +1309,8 @@
         <v>-1.0929274433508813</v>
       </c>
       <c r="N7" s="12">
-        <f>Tabla13[[#This Row],[% día]]+N6</f>
-        <v>-0.27292744335088137</v>
+        <f t="shared" si="0"/>
+        <v>-0.28268143532941564</v>
       </c>
       <c r="O7" s="11" t="s">
         <v>30</v>
@@ -1350,8 +1357,8 @@
         <v>0.10413653456754413</v>
       </c>
       <c r="N8" s="12">
-        <f>Tabla13[[#This Row],[% día]]+N7</f>
-        <v>-0.16879090878333725</v>
+        <f t="shared" si="0"/>
+        <v>-0.17883927541249639</v>
       </c>
       <c r="O8" s="11" t="s">
         <v>32</v>
@@ -1396,8 +1403,8 @@
         <v>0.1830125797067946</v>
       </c>
       <c r="N9" s="12">
-        <f>Tabla13[[#This Row],[% día]]</f>
-        <v>0.1830125797067946</v>
+        <f t="shared" si="0"/>
+        <v>3.8460059228456233E-3</v>
       </c>
       <c r="O9" s="11" t="s">
         <v>35</v>
@@ -1444,14 +1451,60 @@
         <v>-0.28267056380278444</v>
       </c>
       <c r="N10" s="12">
-        <f>Tabla13[[#This Row],[% día]]</f>
-        <v>-0.28267056380278444</v>
+        <f t="shared" si="0"/>
+        <v>-0.27883542940654821</v>
       </c>
       <c r="O10" s="11" t="s">
         <v>37</v>
       </c>
       <c r="P10" s="11" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="10">
+        <f>K10+L10</f>
+        <v>518.57000000000005</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10">
+        <v>1.66</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>521.03</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>0.47438147212526754</v>
+      </c>
+      <c r="N11" s="12">
+        <f t="shared" si="0"/>
+        <v>0.19422329910387887</v>
+      </c>
+      <c r="O11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1471,7 +1524,7 @@
           <x14:formula1>
             <xm:f>Etapas!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B10</xm:sqref>
+          <xm:sqref>B2:B11</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1500,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1573,8 +1626,7 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -1585,11 +1637,11 @@
       </c>
       <c r="G3" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H3" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1766,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1803,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1818,8 +1870,7 @@
         <v>24</v>
       </c>
       <c r="D10">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -1830,11 +1881,11 @@
       </c>
       <c r="G10" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H10" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1976,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2059,11 +2110,10 @@
         <v>31</v>
       </c>
       <c r="D17">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F17" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2071,17 +2121,17 @@
       </c>
       <c r="G17" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H17" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>2.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2100,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F18" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2134,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F19" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2168,7 +2218,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F20" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2202,7 +2252,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2220,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2239,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F22" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2257,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2276,7 +2326,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F23" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2306,11 +2356,10 @@
         <v>38</v>
       </c>
       <c r="D24">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F24" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2318,17 +2367,17 @@
       </c>
       <c r="G24" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H24" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>2.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2347,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F25" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2381,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F26" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2415,7 +2464,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F27" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2449,7 +2498,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F28" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2467,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2486,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F29" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2504,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2523,7 +2572,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F30" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2553,11 +2602,10 @@
         <v>45</v>
       </c>
       <c r="D31">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F31" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2565,11 +2613,11 @@
       </c>
       <c r="G31" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H31" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2591,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F32" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2625,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2659,7 +2707,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2693,7 +2741,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F35" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2727,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F36" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2745,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2764,7 +2812,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F37" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2782,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2797,11 +2845,10 @@
         <v>52</v>
       </c>
       <c r="D38">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F38" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2809,11 +2856,11 @@
       </c>
       <c r="G38" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H38" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2835,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F39" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2869,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F40" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2903,7 +2950,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F41" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2937,7 +2984,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F42" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2971,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F43" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3005,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F44" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3035,11 +3082,10 @@
         <v>59</v>
       </c>
       <c r="D45">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F45" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3047,11 +3093,11 @@
       </c>
       <c r="G45" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H45" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3073,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F46" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3107,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F47" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3141,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F48" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3175,7 +3221,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F49" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3209,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F50" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3243,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F51" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3273,11 +3319,10 @@
         <v>66</v>
       </c>
       <c r="D52">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F52" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3285,11 +3330,11 @@
       </c>
       <c r="G52" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H52" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3311,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F53" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3345,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F54" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3379,7 +3424,7 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F55" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3413,7 +3458,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F56" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3447,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F57" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3481,7 +3526,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F58" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3511,11 +3556,10 @@
         <v>73</v>
       </c>
       <c r="D59">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F59" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3523,11 +3567,11 @@
       </c>
       <c r="G59" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H59" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3549,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F60" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3583,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F61" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3617,7 +3661,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F62" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3651,7 +3695,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F63" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3685,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F64" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3719,7 +3763,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F65" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3749,11 +3793,10 @@
         <v>80</v>
       </c>
       <c r="D66">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F66" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3761,11 +3804,11 @@
       </c>
       <c r="G66" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H66" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3787,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F67" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3821,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F68" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3855,7 +3898,7 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F69" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3889,7 +3932,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F70" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3923,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F71" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3957,7 +4000,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F72" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3987,11 +4030,10 @@
         <v>87</v>
       </c>
       <c r="D73">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F73" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3999,11 +4041,11 @@
       </c>
       <c r="G73" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H73" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -4025,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F74" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4059,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F75" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4093,7 +4135,7 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F76" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4127,7 +4169,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F77" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4161,7 +4203,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F78" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4195,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F79" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4225,11 +4267,10 @@
         <v>94</v>
       </c>
       <c r="D80">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F80" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4237,11 +4278,11 @@
       </c>
       <c r="G80" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H80" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4263,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F81" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4297,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F82" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4331,7 +4372,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F83" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4365,7 +4406,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F84" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4399,7 +4440,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F85" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4433,7 +4474,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F86" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4463,11 +4504,10 @@
         <v>101</v>
       </c>
       <c r="D87">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F87" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4475,11 +4515,11 @@
       </c>
       <c r="G87" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H87" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -4501,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F88" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4535,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F89" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4569,7 +4609,7 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F90" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4603,7 +4643,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F91" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4637,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F92" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4671,7 +4711,7 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F93" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4701,11 +4741,10 @@
         <v>108</v>
       </c>
       <c r="D94">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F94" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4713,11 +4752,11 @@
       </c>
       <c r="G94" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H94" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -4739,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F95" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4773,7 +4812,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F96" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4807,7 +4846,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F97" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4841,7 +4880,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F98" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4875,7 +4914,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F99" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4909,7 +4948,7 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F100" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4939,11 +4978,10 @@
         <v>115</v>
       </c>
       <c r="D101">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F101" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4951,11 +4989,11 @@
       </c>
       <c r="G101" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H101" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -4977,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F102" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5011,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F103" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5045,7 +5083,7 @@
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F104" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5079,7 +5117,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F105" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5113,7 +5151,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F106" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5147,7 +5185,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F107" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5177,11 +5215,10 @@
         <v>122</v>
       </c>
       <c r="D108">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F108" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5189,11 +5226,11 @@
       </c>
       <c r="G108" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H108" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -5215,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F109" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5249,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F110" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5283,7 +5320,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F111" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5317,7 +5354,7 @@
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F112" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5351,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F113" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5385,7 +5422,7 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F114" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5415,11 +5452,10 @@
         <v>129</v>
       </c>
       <c r="D115">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F115" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5427,11 +5463,11 @@
       </c>
       <c r="G115" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H115" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -5453,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F116" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5487,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F117" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5521,7 +5557,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F118" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5555,7 +5591,7 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F119" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5589,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F120" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5623,7 +5659,7 @@
         <v>2</v>
       </c>
       <c r="E121" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F121" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5653,11 +5689,10 @@
         <v>136</v>
       </c>
       <c r="D122">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F122" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5665,11 +5700,11 @@
       </c>
       <c r="G122" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H122" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I122">
         <v>0</v>
@@ -5691,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F123" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5725,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F124" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5759,7 +5794,7 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F125" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5793,7 +5828,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F126" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5827,7 +5862,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F127" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5861,7 +5896,7 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F128" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5891,11 +5926,10 @@
         <v>143</v>
       </c>
       <c r="D129">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F129" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5903,11 +5937,11 @@
       </c>
       <c r="G129" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H129" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -5929,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F130" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5963,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F131" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5997,7 +6031,7 @@
         <v>2</v>
       </c>
       <c r="E132" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F132" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6031,7 +6065,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F133" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6065,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F134" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6099,7 +6133,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F135" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6129,11 +6163,10 @@
         <v>150</v>
       </c>
       <c r="D136">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F136" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6141,11 +6174,11 @@
       </c>
       <c r="G136" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H136" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I136">
         <v>0</v>
@@ -6167,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F137" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6201,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F138" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6235,7 +6268,7 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F139" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6269,7 +6302,7 @@
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F140" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6303,7 +6336,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F141" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6337,7 +6370,7 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F142" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6367,11 +6400,10 @@
         <v>157</v>
       </c>
       <c r="D143">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F143" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6379,11 +6411,11 @@
       </c>
       <c r="G143" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H143" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I143">
         <v>0</v>
@@ -6405,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F144" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6439,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F145" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6473,7 +6505,7 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F146" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6507,7 +6539,7 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F147" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6541,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F148" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6575,7 +6607,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F149" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6605,11 +6637,10 @@
         <v>164</v>
       </c>
       <c r="D150">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F150" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6617,11 +6648,11 @@
       </c>
       <c r="G150" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H150" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I150">
         <v>0</v>
@@ -6643,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F151" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6677,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F152" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6711,7 +6742,7 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F153" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6745,7 +6776,7 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F154" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6779,7 +6810,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F155" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6813,7 +6844,7 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F156" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6843,11 +6874,10 @@
         <v>171</v>
       </c>
       <c r="D157">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F157" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6855,11 +6885,11 @@
       </c>
       <c r="G157" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H157" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -6881,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F158" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6915,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F159" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6949,7 +6979,7 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F160" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6983,7 +7013,7 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F161" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7017,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F162" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7051,7 +7081,7 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F163" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7081,11 +7111,10 @@
         <v>178</v>
       </c>
       <c r="D164">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F164" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7093,11 +7122,11 @@
       </c>
       <c r="G164" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H164" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I164">
         <v>0</v>
@@ -7119,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F165" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7153,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F166" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7187,7 +7216,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F167" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7221,7 +7250,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F168" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7255,7 +7284,7 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F169" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7289,7 +7318,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F170" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7319,11 +7348,10 @@
         <v>185</v>
       </c>
       <c r="D171">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F171" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7331,11 +7359,11 @@
       </c>
       <c r="G171" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H171" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -7357,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F172" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7391,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F173" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7425,7 +7453,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F174" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7459,7 +7487,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F175" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7493,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F176" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7527,7 +7555,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F177" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7557,11 +7585,10 @@
         <v>192</v>
       </c>
       <c r="D178">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F178" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7569,11 +7596,11 @@
       </c>
       <c r="G178" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H178" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I178">
         <v>0</v>
@@ -7595,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F179" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7629,7 +7656,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F180" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7663,7 +7690,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F181" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7697,7 +7724,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F182" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7731,7 +7758,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F183" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7765,7 +7792,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F184" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7795,11 +7822,10 @@
         <v>199</v>
       </c>
       <c r="D185">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F185" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7807,11 +7833,11 @@
       </c>
       <c r="G185" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H185" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -7833,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F186" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7867,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F187" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7901,7 +7927,7 @@
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F188" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7935,7 +7961,7 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F189" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7969,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F190" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8003,7 +8029,7 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F191" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8033,11 +8059,10 @@
         <v>206</v>
       </c>
       <c r="D192">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F192" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8045,11 +8070,11 @@
       </c>
       <c r="G192" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H192" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I192">
         <v>0</v>
@@ -8071,7 +8096,7 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F193" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8105,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F194" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8139,7 +8164,7 @@
         <v>2</v>
       </c>
       <c r="E195" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F195" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8173,7 +8198,7 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F196" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8207,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F197" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8241,7 +8266,7 @@
         <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F198" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8271,11 +8296,10 @@
         <v>213</v>
       </c>
       <c r="D199">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F199" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8283,11 +8307,11 @@
       </c>
       <c r="G199" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H199" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I199">
         <v>0</v>
@@ -8309,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F200" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8343,7 +8367,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F201" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8377,7 +8401,7 @@
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F202" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8411,7 +8435,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F203" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8445,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F204" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8479,7 +8503,7 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F205" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8509,11 +8533,10 @@
         <v>220</v>
       </c>
       <c r="D206">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F206" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8521,11 +8544,11 @@
       </c>
       <c r="G206" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H206" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I206">
         <v>0</v>
@@ -8547,7 +8570,7 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F207" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8581,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F208" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8615,7 +8638,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F209" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8649,7 +8672,7 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F210" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8683,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F211" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8717,7 +8740,7 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F212" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8747,11 +8770,10 @@
         <v>227</v>
       </c>
       <c r="D213">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F213" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8759,11 +8781,11 @@
       </c>
       <c r="G213" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H213" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I213">
         <v>0</v>
@@ -8785,7 +8807,7 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F214" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8819,7 +8841,7 @@
         <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F215" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8853,7 +8875,7 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F216" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8887,7 +8909,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F217" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8921,7 +8943,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F218" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8955,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F219" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8985,11 +9007,10 @@
         <v>234</v>
       </c>
       <c r="D220">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F220" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8997,11 +9018,11 @@
       </c>
       <c r="G220" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H220" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I220">
         <v>0</v>
@@ -9023,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F221" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9057,7 +9078,7 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F222" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9091,7 +9112,7 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F223" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9125,7 +9146,7 @@
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F224" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9159,7 +9180,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F225" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9193,7 +9214,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F226" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9223,11 +9244,10 @@
         <v>241</v>
       </c>
       <c r="D227">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F227" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9235,11 +9255,11 @@
       </c>
       <c r="G227" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H227" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I227">
         <v>0</v>
@@ -9261,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F228" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9295,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F229" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9329,7 +9349,7 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F230" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9363,7 +9383,7 @@
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F231" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9397,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F232" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9431,7 +9451,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F233" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9461,11 +9481,10 @@
         <v>248</v>
       </c>
       <c r="D234">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F234" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9473,11 +9492,11 @@
       </c>
       <c r="G234" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H234" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I234">
         <v>0</v>
@@ -9499,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F235" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9533,7 +9552,7 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F236" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9567,7 +9586,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F237" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9601,7 +9620,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F238" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9635,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F239" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9669,7 +9688,7 @@
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F240" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9699,11 +9718,10 @@
         <v>255</v>
       </c>
       <c r="D241">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F241" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9711,11 +9729,11 @@
       </c>
       <c r="G241" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H241" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I241">
         <v>0</v>
@@ -9737,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="E242" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F242" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9771,7 +9789,7 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F243" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9805,7 +9823,7 @@
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F244" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9839,7 +9857,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F245" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9873,7 +9891,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F246" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9907,7 +9925,7 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F247" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9937,11 +9955,10 @@
         <v>262</v>
       </c>
       <c r="D248">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F248" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9949,11 +9966,11 @@
       </c>
       <c r="G248" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H248" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I248">
         <v>0</v>
@@ -9975,7 +9992,7 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F249" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10009,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F250" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10043,7 +10060,7 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F251" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10077,7 +10094,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F252" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10111,7 +10128,7 @@
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F253" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10145,7 +10162,7 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F254" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10175,11 +10192,10 @@
         <v>269</v>
       </c>
       <c r="D255">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E255" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F255" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10187,11 +10203,11 @@
       </c>
       <c r="G255" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H255" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -10213,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F256" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10247,7 +10263,7 @@
         <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F257" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10281,7 +10297,7 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F258" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10315,7 +10331,7 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F259" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10349,7 +10365,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F260" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10383,7 +10399,7 @@
         <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F261" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10413,11 +10429,10 @@
         <v>276</v>
       </c>
       <c r="D262">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F262" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10425,11 +10440,11 @@
       </c>
       <c r="G262" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H262" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I262">
         <v>0</v>
@@ -10451,7 +10466,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F263" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10485,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F264" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10519,7 +10534,7 @@
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F265" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10553,7 +10568,7 @@
         <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F266" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10587,7 +10602,7 @@
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F267" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10621,7 +10636,7 @@
         <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F268" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10651,11 +10666,10 @@
         <v>283</v>
       </c>
       <c r="D269">
-        <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Dia Semana]],Riesgo!A:A,Riesgo!B:B)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F269" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10663,11 +10677,11 @@
       </c>
       <c r="G269" s="17">
         <f>Tabla3[[#This Row],[% Op. Etapa]]*Tabla3[[#This Row],[Ratio]]</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="H269" s="17">
         <f>IF(Tabla3[[#This Row],[Noticia]]&gt;0,Tabla3[[#This Row],[% Esperado]]/2,Tabla3[[#This Row],[% Esperado]])</f>
-        <v>3.5000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="I269">
         <v>0</v>
@@ -10689,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F270" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10723,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F271" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10774,15 +10788,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -10790,7 +10804,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10798,7 +10812,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -10806,7 +10820,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10814,7 +10828,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -10822,7 +10836,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10830,7 +10844,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10861,31 +10875,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -10914,12 +10928,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B3" s="17">
         <v>5.0000000000000001E-3</v>
@@ -10943,12 +10957,12 @@
         <v>0.4</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B4" s="17">
         <v>3.5000000000000001E-3</v>
@@ -10972,12 +10986,12 @@
         <v>0.5</v>
       </c>
       <c r="I4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11001,12 +11015,12 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11030,12 +11044,12 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B7" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11059,7 +11073,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DD039AD-051E-4A3F-ADB2-4695708B15A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56752291-E8DF-4C62-A7C3-CE1F43B2D3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56752291-E8DF-4C62-A7C3-CE1F43B2D3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{49052AD8-4AE6-4A82-8881-D9C40EE0FFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>Mi paciencia es mi ventaja: actúo solo cuando mis reglas lo confirman.</t>
+  </si>
+  <si>
+    <t>PPA 81, PA 105.  No se ingresa por reglas.</t>
+  </si>
+  <si>
+    <t>Elijo la calma y confío en mis reglas: cuando el mercado se mueve con ruido, espero la señal que mi plan confirma.</t>
   </si>
   <si>
     <t>Dia Semana</t>
@@ -606,8 +612,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P11" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:P11" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P12" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
+  <autoFilter ref="A1:P12" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
@@ -991,7 +997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
@@ -1507,6 +1513,52 @@
         <v>40</v>
       </c>
     </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="10">
+        <f>K11+L11</f>
+        <v>521.03</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="H12" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>522.67999999999995</v>
+      </c>
+      <c r="L12" s="10"/>
+      <c r="M12" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>0.31668042147285186</v>
+      </c>
+      <c r="N12" s="12">
+        <f>(K12-$C$2)/($C$2)*100</f>
+        <v>0.51151878773892701</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
     <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
@@ -1524,7 +1576,7 @@
           <x14:formula1>
             <xm:f>Etapas!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B11</xm:sqref>
+          <xm:sqref>B2:B12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1553,31 +1605,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1818,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1855,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2027,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2113,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F17" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2131,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2150,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F18" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2184,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F19" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2218,7 +2270,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F20" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2252,7 +2304,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F21" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2270,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2289,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F22" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2307,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2326,7 +2378,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F23" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2359,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F24" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2377,7 +2429,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2396,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F25" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2430,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F26" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2464,7 +2516,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F27" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2498,7 +2550,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F28" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2516,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2535,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F29" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2553,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2572,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F30" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2605,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F31" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2639,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F32" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2673,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2707,7 +2759,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2741,7 +2793,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F35" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2775,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F36" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2793,7 +2845,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2812,7 +2864,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F37" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2830,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2848,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F38" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2882,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F39" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2916,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F40" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2950,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F41" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2984,7 +3036,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F42" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3018,7 +3070,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F43" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3052,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F44" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3085,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F45" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3119,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F46" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3153,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F47" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3187,7 +3239,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F48" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3221,7 +3273,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F49" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3255,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F50" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3289,7 +3341,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F51" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3322,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F52" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3356,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F53" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3390,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F54" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3424,7 +3476,7 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F55" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3458,7 +3510,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F56" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3492,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F57" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3526,7 +3578,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F58" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3559,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F59" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3593,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F60" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3627,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F61" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3661,7 +3713,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F62" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3695,7 +3747,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F63" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3729,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F64" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3763,7 +3815,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F65" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3796,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F66" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3830,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F67" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3864,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F68" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3898,7 +3950,7 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F69" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3932,7 +3984,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F70" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3966,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F71" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4000,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F72" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4033,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F73" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4067,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F74" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4101,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F75" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4135,7 +4187,7 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F76" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4169,7 +4221,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F77" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4203,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F78" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4237,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F79" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4270,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F80" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4304,7 +4356,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F81" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4338,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F82" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4372,7 +4424,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F83" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4406,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F84" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4440,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F85" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4474,7 +4526,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F86" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4507,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F87" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4541,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F88" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4575,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F89" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4609,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F90" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4643,7 +4695,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F91" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4677,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F92" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4711,7 +4763,7 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F93" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4744,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F94" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4778,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F95" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4812,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F96" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4846,7 +4898,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F97" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4880,7 +4932,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F98" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4914,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F99" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4948,7 +5000,7 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F100" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4981,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F101" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5015,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F102" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5049,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F103" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5083,7 +5135,7 @@
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F104" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5117,7 +5169,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F105" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5151,7 +5203,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F106" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5185,7 +5237,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F107" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5218,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F108" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5252,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F109" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5286,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F110" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5320,7 +5372,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F111" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5354,7 +5406,7 @@
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F112" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5388,7 +5440,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F113" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5422,7 +5474,7 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F114" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5455,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F115" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5489,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F116" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5523,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F117" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5557,7 +5609,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F118" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5591,7 +5643,7 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F119" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5625,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F120" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5659,7 +5711,7 @@
         <v>2</v>
       </c>
       <c r="E121" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F121" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5692,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F122" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5726,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F123" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5760,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F124" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5794,7 +5846,7 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F125" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5828,7 +5880,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F126" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5862,7 +5914,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F127" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5896,7 +5948,7 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F128" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5929,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F129" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5963,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F130" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5997,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F131" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6031,7 +6083,7 @@
         <v>2</v>
       </c>
       <c r="E132" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F132" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6065,7 +6117,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F133" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6099,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F134" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6133,7 +6185,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F135" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6166,7 +6218,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F136" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6200,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F137" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6234,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F138" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6268,7 +6320,7 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F139" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6302,7 +6354,7 @@
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F140" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6336,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F141" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6370,7 +6422,7 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F142" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6403,7 +6455,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F143" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6437,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F144" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6471,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F145" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6505,7 +6557,7 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F146" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6539,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F147" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6573,7 +6625,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F148" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6607,7 +6659,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F149" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6640,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F150" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6674,7 +6726,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F151" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6708,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F152" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6742,7 +6794,7 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F153" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6776,7 +6828,7 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F154" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6810,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F155" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6844,7 +6896,7 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F156" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6877,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F157" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6911,7 +6963,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F158" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6945,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F159" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6979,7 +7031,7 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F160" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7013,7 +7065,7 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F161" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7047,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F162" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7081,7 +7133,7 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F163" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7114,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F164" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7148,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F165" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7182,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F166" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7216,7 +7268,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F167" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7250,7 +7302,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F168" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7284,7 +7336,7 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F169" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7318,7 +7370,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F170" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7351,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F171" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7385,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F172" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7419,7 +7471,7 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F173" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7453,7 +7505,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F174" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7487,7 +7539,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F175" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7521,7 +7573,7 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F176" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7555,7 +7607,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F177" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7588,7 +7640,7 @@
         <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F178" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7622,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F179" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7656,7 +7708,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F180" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7690,7 +7742,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F181" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7724,7 +7776,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F182" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7758,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F183" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7792,7 +7844,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F184" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7825,7 +7877,7 @@
         <v>0</v>
       </c>
       <c r="E185" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F185" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7859,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F186" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7893,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F187" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7927,7 +7979,7 @@
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F188" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7961,7 +8013,7 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F189" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7995,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F190" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8029,7 +8081,7 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F191" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8062,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F192" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8096,7 +8148,7 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F193" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8130,7 +8182,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F194" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8164,7 +8216,7 @@
         <v>2</v>
       </c>
       <c r="E195" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F195" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8198,7 +8250,7 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F196" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8232,7 +8284,7 @@
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F197" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8266,7 +8318,7 @@
         <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F198" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8299,7 +8351,7 @@
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F199" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8333,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F200" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8367,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F201" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8401,7 +8453,7 @@
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F202" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8435,7 +8487,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F203" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8469,7 +8521,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F204" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8503,7 +8555,7 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F205" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8536,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F206" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8570,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F207" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8604,7 +8656,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F208" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8638,7 +8690,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F209" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8672,7 +8724,7 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F210" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8706,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F211" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8740,7 +8792,7 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F212" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8773,7 +8825,7 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F213" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8807,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F214" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8841,7 +8893,7 @@
         <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F215" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8875,7 +8927,7 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F216" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8909,7 +8961,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F217" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8943,7 +8995,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F218" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8977,7 +9029,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F219" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9010,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F220" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9044,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F221" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9078,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F222" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9112,7 +9164,7 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F223" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9146,7 +9198,7 @@
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F224" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9180,7 +9232,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F225" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9214,7 +9266,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F226" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9247,7 +9299,7 @@
         <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F227" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9281,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F228" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9315,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F229" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9349,7 +9401,7 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F230" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9383,7 +9435,7 @@
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F231" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9417,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F232" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9451,7 +9503,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F233" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9484,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F234" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9518,7 +9570,7 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F235" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9552,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F236" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9586,7 +9638,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F237" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9620,7 +9672,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F238" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9654,7 +9706,7 @@
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F239" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9688,7 +9740,7 @@
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F240" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9721,7 +9773,7 @@
         <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F241" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9755,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="E242" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F242" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9789,7 +9841,7 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F243" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9823,7 +9875,7 @@
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F244" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9857,7 +9909,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F245" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9891,7 +9943,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F246" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9925,7 +9977,7 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F247" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9958,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="E248" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F248" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9992,7 +10044,7 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F249" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10026,7 +10078,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F250" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10060,7 +10112,7 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F251" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10094,7 +10146,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F252" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10128,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F253" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10162,7 +10214,7 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F254" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10195,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F255" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10229,7 +10281,7 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F256" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10263,7 +10315,7 @@
         <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F257" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10297,7 +10349,7 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F258" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10331,7 +10383,7 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F259" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10365,7 +10417,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F260" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10399,7 +10451,7 @@
         <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F261" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10432,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F262" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10466,7 +10518,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F263" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10500,7 +10552,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F264" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10534,7 +10586,7 @@
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F265" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10568,7 +10620,7 @@
         <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F266" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10602,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F267" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10636,7 +10688,7 @@
         <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F268" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10669,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F269" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10703,7 +10755,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F270" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10737,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F271" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10788,15 +10840,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -10804,7 +10856,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10812,7 +10864,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -10820,7 +10872,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10828,7 +10880,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -10836,7 +10888,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10844,7 +10896,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10875,31 +10927,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -10928,12 +10980,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="17">
         <v>5.0000000000000001E-3</v>
@@ -10957,12 +11009,12 @@
         <v>0.4</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" s="17">
         <v>3.5000000000000001E-3</v>
@@ -10986,12 +11038,12 @@
         <v>0.5</v>
       </c>
       <c r="I4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11015,12 +11067,12 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B6" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11044,12 +11096,12 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B7" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11073,7 +11125,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49052AD8-4AE6-4A82-8881-D9C40EE0FFAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{700C851B-6E2C-42AB-8D03-753E7D6C87CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="90">
   <si>
     <t>Fecha</t>
   </si>
@@ -316,9 +316,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -423,7 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -455,6 +456,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -612,8 +614,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P12" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:P12" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P13" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
+  <autoFilter ref="A1:P13" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
@@ -997,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
@@ -1559,6 +1561,40 @@
         <v>42</v>
       </c>
     </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="10">
+        <f>K12+L12</f>
+        <v>522.67999999999995</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>522.67999999999995</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="12">
+        <f>(K13-$C$2)/($C$2)*100</f>
+        <v>0.51151878773892701</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
     <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
@@ -1576,7 +1612,7 @@
           <x14:formula1>
             <xm:f>Etapas!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B12</xm:sqref>
+          <xm:sqref>B2:B13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10973,8 +11009,8 @@
       <c r="F2">
         <v>60</v>
       </c>
-      <c r="G2" s="16">
-        <v>7.0000000000000007E-2</v>
+      <c r="G2" s="21">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H2" s="16">
         <v>0</v>
@@ -11002,8 +11038,8 @@
       <c r="F3">
         <v>70</v>
       </c>
-      <c r="G3" s="16">
-        <v>7.0000000000000007E-2</v>
+      <c r="G3" s="21">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H3" s="16">
         <v>0.4</v>
@@ -11031,8 +11067,8 @@
       <c r="F4">
         <v>90</v>
       </c>
-      <c r="G4" s="16">
-        <v>7.0000000000000007E-2</v>
+      <c r="G4" s="21">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H4" s="16">
         <v>0.5</v>
@@ -11060,8 +11096,8 @@
       <c r="F5">
         <v>90</v>
       </c>
-      <c r="G5" s="16">
-        <v>7.0000000000000007E-2</v>
+      <c r="G5" s="21">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H5" s="16">
         <v>0.6</v>
@@ -11089,8 +11125,8 @@
       <c r="F6">
         <v>90</v>
       </c>
-      <c r="G6" s="16">
-        <v>7.0000000000000007E-2</v>
+      <c r="G6" s="21">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H6" s="16">
         <v>0.7</v>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30619"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{700C851B-6E2C-42AB-8D03-753E7D6C87CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BA2AE27-C63C-41B7-9433-09FE9A197EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
   <si>
     <t>Fecha</t>
   </si>
@@ -169,6 +169,12 @@
   </si>
   <si>
     <t>Elijo la calma y confío en mis reglas: cuando el mercado se mueve con ruido, espero la señal que mi plan confirma.</t>
+  </si>
+  <si>
+    <t>PA 70, No se ingresa por reglas</t>
+  </si>
+  <si>
+    <t>Confío en mi plan y lo sigo con serenidad: cada decisión alineada con mis reglas construye mi camino.</t>
   </si>
   <si>
     <t>Dia Semana</t>
@@ -1572,28 +1578,40 @@
         <f>K12+L12</f>
         <v>522.67999999999995</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="D13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+      <c r="G13" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="H13" s="10">
+        <v>1.5</v>
+      </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10">
         <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
-        <v>522.67999999999995</v>
+        <v>523.78</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="14">
         <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
-        <v>0</v>
+        <v>0.21045381495370022</v>
       </c>
       <c r="N13" s="12">
         <f>(K13-$C$2)/($C$2)*100</f>
-        <v>0.51151878773892701</v>
-      </c>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
+        <v>0.72304911349563306</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
@@ -1641,31 +1659,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1906,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1943,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2115,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2201,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F17" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2219,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2238,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F18" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2272,7 +2290,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F19" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2306,7 +2324,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F20" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2340,7 +2358,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F21" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2358,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2377,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F22" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2395,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2414,7 +2432,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F23" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2447,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F24" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2465,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2484,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F25" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2518,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F26" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2552,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F27" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2586,7 +2604,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F28" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2604,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2623,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F29" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2641,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2660,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F30" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2693,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F31" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2727,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F32" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2761,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2795,7 +2813,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2829,7 +2847,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F35" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2863,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F36" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2881,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2900,7 +2918,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F37" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2918,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2936,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F38" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2970,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F39" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3004,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F40" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3038,7 +3056,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F41" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3072,7 +3090,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F42" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3106,7 +3124,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F43" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3140,7 +3158,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F44" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3173,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F45" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3207,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F46" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3241,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F47" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3275,7 +3293,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F48" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3309,7 +3327,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F49" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3343,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F50" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3377,7 +3395,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F51" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3410,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F52" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3444,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F53" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3478,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F54" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3512,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F55" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3546,7 +3564,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F56" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3580,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F57" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3614,7 +3632,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F58" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3647,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F59" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3681,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F60" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3715,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F61" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3749,7 +3767,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F62" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3783,7 +3801,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F63" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3817,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F64" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3851,7 +3869,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F65" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3884,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F66" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3918,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F67" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3952,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F68" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3986,7 +4004,7 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F69" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4020,7 +4038,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F70" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4054,7 +4072,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F71" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4088,7 +4106,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F72" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4121,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F73" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4155,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F74" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4189,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F75" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4223,7 +4241,7 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F76" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4257,7 +4275,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F77" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4291,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F78" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4325,7 +4343,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F79" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4358,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F80" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4392,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F81" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4426,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F82" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4460,7 +4478,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F83" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4494,7 +4512,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F84" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4528,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F85" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4562,7 +4580,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F86" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4595,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F87" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4629,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F88" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4663,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F89" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4697,7 +4715,7 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F90" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4731,7 +4749,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F91" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4765,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F92" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4799,7 +4817,7 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F93" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4832,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F94" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4866,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F95" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4900,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F96" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4934,7 +4952,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F97" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4968,7 +4986,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F98" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5002,7 +5020,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F99" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5036,7 +5054,7 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F100" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5069,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F101" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5103,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F102" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5137,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F103" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5171,7 +5189,7 @@
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F104" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5205,7 +5223,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F105" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5239,7 +5257,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F106" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5273,7 +5291,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F107" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5306,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F108" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5340,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F109" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5374,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F110" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5408,7 +5426,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F111" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5442,7 +5460,7 @@
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F112" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5476,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F113" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5510,7 +5528,7 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F114" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5543,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F115" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5577,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F116" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5611,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F117" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5645,7 +5663,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F118" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5679,7 +5697,7 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F119" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5713,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F120" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5747,7 +5765,7 @@
         <v>2</v>
       </c>
       <c r="E121" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F121" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5780,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F122" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5814,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F123" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5848,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F124" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5882,7 +5900,7 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F125" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5916,7 +5934,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F126" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5950,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F127" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5984,7 +6002,7 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F128" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6017,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F129" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6051,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F130" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6085,7 +6103,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F131" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6119,7 +6137,7 @@
         <v>2</v>
       </c>
       <c r="E132" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F132" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6153,7 +6171,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F133" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6187,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F134" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6221,7 +6239,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F135" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6254,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F136" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6288,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F137" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6322,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F138" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6356,7 +6374,7 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F139" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6390,7 +6408,7 @@
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F140" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6424,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F141" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6458,7 +6476,7 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F142" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6491,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F143" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6525,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F144" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6559,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F145" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6593,7 +6611,7 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F146" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6627,7 +6645,7 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F147" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6661,7 +6679,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F148" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6695,7 +6713,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F149" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6728,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F150" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6762,7 +6780,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F151" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6796,7 +6814,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F152" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6830,7 +6848,7 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F153" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6864,7 +6882,7 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F154" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6898,7 +6916,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F155" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6932,7 +6950,7 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F156" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6965,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F157" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6999,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F158" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7033,7 +7051,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F159" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7067,7 +7085,7 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F160" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7101,7 +7119,7 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F161" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7135,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F162" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7169,7 +7187,7 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F163" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7202,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F164" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7236,7 +7254,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F165" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7270,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F166" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7304,7 +7322,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F167" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7338,7 +7356,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F168" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7372,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F169" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7406,7 +7424,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F170" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7439,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F171" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7473,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F172" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7507,7 +7525,7 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F173" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7541,7 +7559,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F174" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7575,7 +7593,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F175" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7609,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F176" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7643,7 +7661,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F177" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7676,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F178" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7710,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F179" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7744,7 +7762,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F180" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7778,7 +7796,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F181" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7812,7 +7830,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F182" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7846,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F183" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7880,7 +7898,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F184" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7913,7 +7931,7 @@
         <v>0</v>
       </c>
       <c r="E185" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F185" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7947,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F186" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7981,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F187" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8015,7 +8033,7 @@
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F188" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8049,7 +8067,7 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F189" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8083,7 +8101,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F190" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8117,7 +8135,7 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F191" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8150,7 +8168,7 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F192" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8184,7 +8202,7 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F193" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8218,7 +8236,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F194" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8252,7 +8270,7 @@
         <v>2</v>
       </c>
       <c r="E195" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F195" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8286,7 +8304,7 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F196" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8320,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F197" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8354,7 +8372,7 @@
         <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F198" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8387,7 +8405,7 @@
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F199" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8421,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F200" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8455,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F201" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8489,7 +8507,7 @@
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F202" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8523,7 +8541,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F203" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8557,7 +8575,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F204" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8591,7 +8609,7 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F205" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8624,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F206" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8658,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F207" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8692,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F208" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8726,7 +8744,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F209" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8760,7 +8778,7 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F210" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8794,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F211" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8828,7 +8846,7 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F212" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8861,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F213" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8895,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F214" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8929,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F215" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8963,7 +8981,7 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F216" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8997,7 +9015,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F217" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9031,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F218" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9065,7 +9083,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F219" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9098,7 +9116,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F220" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9132,7 +9150,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F221" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9166,7 +9184,7 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F222" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9200,7 +9218,7 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F223" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9234,7 +9252,7 @@
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F224" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9268,7 +9286,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F225" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9302,7 +9320,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F226" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9335,7 +9353,7 @@
         <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F227" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9369,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F228" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9403,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F229" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9437,7 +9455,7 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F230" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9471,7 +9489,7 @@
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F231" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9505,7 +9523,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F232" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9539,7 +9557,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F233" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9572,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F234" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9606,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F235" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9640,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F236" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9674,7 +9692,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F237" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9708,7 +9726,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F238" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9742,7 +9760,7 @@
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F239" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9776,7 +9794,7 @@
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F240" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9809,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F241" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9843,7 +9861,7 @@
         <v>0</v>
       </c>
       <c r="E242" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F242" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9877,7 +9895,7 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F243" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9911,7 +9929,7 @@
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F244" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9945,7 +9963,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F245" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9979,7 +9997,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F246" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10013,7 +10031,7 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F247" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10046,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="E248" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F248" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10080,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F249" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10114,7 +10132,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F250" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10148,7 +10166,7 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F251" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10182,7 +10200,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F252" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10216,7 +10234,7 @@
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F253" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10250,7 +10268,7 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F254" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10283,7 +10301,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F255" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10317,7 +10335,7 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F256" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10351,7 +10369,7 @@
         <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F257" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10385,7 +10403,7 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F258" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10419,7 +10437,7 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F259" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10453,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F260" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10487,7 +10505,7 @@
         <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F261" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10520,7 +10538,7 @@
         <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F262" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10554,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F263" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10588,7 +10606,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F264" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10622,7 +10640,7 @@
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F265" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10656,7 +10674,7 @@
         <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F266" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10690,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F267" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10724,7 +10742,7 @@
         <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F268" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10757,7 +10775,7 @@
         <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F269" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10791,7 +10809,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F270" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10825,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F271" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10876,15 +10894,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -10892,7 +10910,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10900,7 +10918,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -10908,7 +10926,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10916,7 +10934,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -10924,7 +10942,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10932,7 +10950,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10963,31 +10981,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11016,12 +11034,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B3" s="17">
         <v>5.0000000000000001E-3</v>
@@ -11045,12 +11063,12 @@
         <v>0.4</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B4" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11074,12 +11092,12 @@
         <v>0.5</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11103,12 +11121,12 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B6" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11132,12 +11150,12 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11161,7 +11179,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30619"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BA2AE27-C63C-41B7-9433-09FE9A197EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89DA7DB1-8D34-49F3-9768-02DC8D8A588E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="95">
   <si>
     <t>Fecha</t>
   </si>
@@ -175,6 +175,15 @@
   </si>
   <si>
     <t>Confío en mi plan y lo sigo con serenidad: cada decisión alineada con mis reglas construye mi camino.</t>
+  </si>
+  <si>
+    <t>Decisión de entrada por reglas, desde el inicio se determina el riesgo</t>
+  </si>
+  <si>
+    <t>Acepto cada resultado con calma, porque mi stop protege mi cuenta y mi plan sigue en pie.</t>
+  </si>
+  <si>
+    <t>No se controlo el ego de quererle ganar al mercado con los ajustes, me gano la emoción, prometo no sumar operativas a los ajsutes, el bot lo tengo con 2 se queda con 2 y acepto la perdida y dejo atras querer tener la razón</t>
   </si>
   <si>
     <t>Dia Semana</t>
@@ -620,8 +629,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P13" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:P13" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P15" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
+  <autoFilter ref="A1:P15" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
@@ -1005,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
@@ -1613,6 +1622,95 @@
         <v>44</v>
       </c>
     </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <f>K13+L13</f>
+        <v>523.78</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="10">
+        <v>-10.78</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>513</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>-2.0581160029019818</v>
+      </c>
+      <c r="N14" s="12">
+        <f>(K14-$C$2)/($C$2)*100</f>
+        <v>-1.3499480789200382</v>
+      </c>
+      <c r="O14" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <f>K14+L14</f>
+        <v>513</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10">
+        <v>-1.98</v>
+      </c>
+      <c r="H15" s="10">
+        <f>-0.13-0.09-0.17</f>
+        <v>-0.39</v>
+      </c>
+      <c r="I15" s="10">
+        <v>-2.2799999999999998</v>
+      </c>
+      <c r="J15" s="10">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>509.35</v>
+      </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>-0.71150097465886952</v>
+      </c>
+      <c r="N15" s="12">
+        <f>(K15-$C$2)/($C$2)*100</f>
+        <v>-2.0518441598399986</v>
+      </c>
+      <c r="O15" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="P15" s="11"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
     <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
@@ -1630,7 +1728,7 @@
           <x14:formula1>
             <xm:f>Etapas!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B13</xm:sqref>
+          <xm:sqref>B2:B15</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1659,31 +1757,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1924,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1961,7 +2059,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2133,7 +2231,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2219,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F17" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2237,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2256,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F18" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2290,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F19" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2324,7 +2422,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F20" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2358,7 +2456,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F21" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2376,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2395,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F22" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2413,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2432,7 +2530,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F23" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2465,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F24" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2483,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2502,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F25" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2536,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F26" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2570,7 +2668,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F27" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2604,7 +2702,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F28" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2622,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2641,7 +2739,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F29" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2659,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2678,7 +2776,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F30" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2711,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F31" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2745,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F32" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2779,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2813,7 +2911,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2847,7 +2945,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F35" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2881,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F36" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2899,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2918,7 +3016,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F37" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2936,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2954,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F38" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2988,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F39" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3022,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F40" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3056,7 +3154,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F41" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3090,7 +3188,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F42" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3124,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F43" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3158,7 +3256,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F44" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3191,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F45" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3225,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F46" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3259,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F47" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3293,7 +3391,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F48" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3327,7 +3425,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F49" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3361,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F50" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3395,7 +3493,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F51" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3428,7 +3526,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F52" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3462,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F53" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3496,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F54" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3530,7 +3628,7 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F55" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3564,7 +3662,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F56" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3598,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F57" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3632,7 +3730,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F58" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3665,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F59" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3699,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F60" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3733,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F61" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3767,7 +3865,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F62" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3801,7 +3899,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F63" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3835,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F64" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3869,7 +3967,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F65" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3902,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F66" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3936,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F67" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3970,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F68" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4004,7 +4102,7 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F69" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4038,7 +4136,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F70" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4072,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F71" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4106,7 +4204,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F72" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4139,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F73" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4173,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F74" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4207,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F75" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4241,7 +4339,7 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F76" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4275,7 +4373,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F77" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4309,7 +4407,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F78" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4343,7 +4441,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F79" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4376,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F80" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4410,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F81" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4444,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F82" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4478,7 +4576,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F83" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4512,7 +4610,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F84" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4546,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F85" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4580,7 +4678,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F86" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4613,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F87" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4647,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F88" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4681,7 +4779,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F89" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4715,7 +4813,7 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F90" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4749,7 +4847,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F91" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4783,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F92" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4817,7 +4915,7 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F93" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4850,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F94" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4884,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F95" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4918,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F96" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4952,7 +5050,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F97" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4986,7 +5084,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F98" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5020,7 +5118,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F99" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5054,7 +5152,7 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F100" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5087,7 +5185,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F101" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5121,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F102" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5155,7 +5253,7 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F103" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5189,7 +5287,7 @@
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F104" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5223,7 +5321,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F105" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5257,7 +5355,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F106" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5291,7 +5389,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F107" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5324,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F108" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5358,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F109" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5392,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F110" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5426,7 +5524,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F111" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5460,7 +5558,7 @@
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F112" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5494,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F113" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5528,7 +5626,7 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F114" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5561,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F115" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5595,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F116" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5629,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F117" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5663,7 +5761,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F118" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5697,7 +5795,7 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F119" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5731,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F120" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5765,7 +5863,7 @@
         <v>2</v>
       </c>
       <c r="E121" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F121" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5798,7 +5896,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F122" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5832,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F123" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5866,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F124" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5900,7 +5998,7 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F125" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5934,7 +6032,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F126" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5968,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F127" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6002,7 +6100,7 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F128" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6035,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F129" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6069,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F130" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6103,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F131" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6137,7 +6235,7 @@
         <v>2</v>
       </c>
       <c r="E132" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F132" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6171,7 +6269,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F133" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6205,7 +6303,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F134" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6239,7 +6337,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F135" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6272,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F136" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6306,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F137" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6340,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F138" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6374,7 +6472,7 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F139" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6408,7 +6506,7 @@
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F140" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6442,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F141" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6476,7 +6574,7 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F142" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6509,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F143" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6543,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F144" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6577,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F145" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6611,7 +6709,7 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F146" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6645,7 +6743,7 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F147" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6679,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F148" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6713,7 +6811,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F149" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6746,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F150" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6780,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F151" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6814,7 +6912,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F152" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6848,7 +6946,7 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F153" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6882,7 +6980,7 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F154" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6916,7 +7014,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F155" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6950,7 +7048,7 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F156" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6983,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F157" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7017,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F158" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7051,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F159" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7085,7 +7183,7 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F160" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7119,7 +7217,7 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F161" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7153,7 +7251,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F162" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7187,7 +7285,7 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F163" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7220,7 +7318,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F164" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7254,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F165" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7288,7 +7386,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F166" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7322,7 +7420,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F167" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7356,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F168" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7390,7 +7488,7 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F169" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7424,7 +7522,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F170" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7457,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F171" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7491,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F172" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7525,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F173" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7559,7 +7657,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F174" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7593,7 +7691,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F175" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7627,7 +7725,7 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F176" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7661,7 +7759,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F177" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7694,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F178" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7728,7 +7826,7 @@
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F179" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7762,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F180" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7796,7 +7894,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F181" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7830,7 +7928,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F182" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7864,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F183" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7898,7 +7996,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F184" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7931,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="E185" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F185" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7965,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F186" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7999,7 +8097,7 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F187" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8033,7 +8131,7 @@
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F188" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8067,7 +8165,7 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F189" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8101,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F190" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8135,7 +8233,7 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F191" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8168,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F192" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8202,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F193" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8236,7 +8334,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F194" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8270,7 +8368,7 @@
         <v>2</v>
       </c>
       <c r="E195" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F195" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8304,7 +8402,7 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F196" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8338,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F197" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8372,7 +8470,7 @@
         <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F198" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8405,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F199" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8439,7 +8537,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F200" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8473,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F201" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8507,7 +8605,7 @@
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F202" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8541,7 +8639,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F203" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8575,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F204" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8609,7 +8707,7 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F205" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8642,7 +8740,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F206" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8676,7 +8774,7 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F207" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8710,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F208" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8744,7 +8842,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F209" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8778,7 +8876,7 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F210" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8812,7 +8910,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F211" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8846,7 +8944,7 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F212" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8879,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F213" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8913,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F214" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8947,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F215" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8981,7 +9079,7 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F216" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9015,7 +9113,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F217" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9049,7 +9147,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F218" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9083,7 +9181,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F219" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9116,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F220" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9150,7 +9248,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F221" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9184,7 +9282,7 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F222" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9218,7 +9316,7 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F223" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9252,7 +9350,7 @@
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F224" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9286,7 +9384,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F225" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9320,7 +9418,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F226" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9353,7 +9451,7 @@
         <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F227" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9387,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F228" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9421,7 +9519,7 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F229" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9455,7 +9553,7 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F230" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9489,7 +9587,7 @@
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F231" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9523,7 +9621,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F232" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9557,7 +9655,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F233" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9590,7 +9688,7 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F234" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9624,7 +9722,7 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F235" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9658,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F236" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9692,7 +9790,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F237" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9726,7 +9824,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F238" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9760,7 +9858,7 @@
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F239" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9794,7 +9892,7 @@
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F240" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9827,7 +9925,7 @@
         <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F241" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9861,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="E242" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F242" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9895,7 +9993,7 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F243" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9929,7 +10027,7 @@
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F244" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9963,7 +10061,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F245" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9997,7 +10095,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F246" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10031,7 +10129,7 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F247" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10064,7 +10162,7 @@
         <v>0</v>
       </c>
       <c r="E248" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F248" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10098,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F249" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10132,7 +10230,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F250" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10166,7 +10264,7 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F251" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10200,7 +10298,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F252" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10234,7 +10332,7 @@
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F253" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10268,7 +10366,7 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F254" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10301,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F255" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10335,7 +10433,7 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F256" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10369,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F257" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10403,7 +10501,7 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F258" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10437,7 +10535,7 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F259" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10471,7 +10569,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F260" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10505,7 +10603,7 @@
         <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F261" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10538,7 +10636,7 @@
         <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F262" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10572,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F263" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10606,7 +10704,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F264" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10640,7 +10738,7 @@
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F265" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10674,7 +10772,7 @@
         <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F266" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10708,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F267" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10742,7 +10840,7 @@
         <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F268" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10775,7 +10873,7 @@
         <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F269" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10809,7 +10907,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F270" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10843,7 +10941,7 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F271" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10894,15 +10992,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -10910,7 +11008,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -10918,7 +11016,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -10926,7 +11024,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -10934,7 +11032,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -10942,7 +11040,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -10950,7 +11048,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -10981,31 +11079,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11034,12 +11132,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B3" s="17">
         <v>5.0000000000000001E-3</v>
@@ -11063,12 +11161,12 @@
         <v>0.4</v>
       </c>
       <c r="I3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B4" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11092,12 +11190,12 @@
         <v>0.5</v>
       </c>
       <c r="I4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B5" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11121,12 +11219,12 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B6" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11150,12 +11248,12 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B7" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11179,7 +11277,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30619"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89DA7DB1-8D34-49F3-9768-02DC8D8A588E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A608E9-4926-412D-A281-A4900027C4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="96">
   <si>
     <t>Fecha</t>
   </si>
@@ -177,13 +177,16 @@
     <t>Confío en mi plan y lo sigo con serenidad: cada decisión alineada con mis reglas construye mi camino.</t>
   </si>
   <si>
-    <t>Decisión de entrada por reglas, desde el inicio se determina el riesgo</t>
+    <t>Decisión de entrada por reglas, desde el inicio se determina el riesgo, igual me habia dicho que en estas noticias iba al mitad del riesgo y no lo hice por la alta volatilidad</t>
   </si>
   <si>
     <t>Acepto cada resultado con calma, porque mi stop protege mi cuenta y mi plan sigue en pie.</t>
   </si>
   <si>
-    <t>No se controlo el ego de quererle ganar al mercado con los ajustes, me gano la emoción, prometo no sumar operativas a los ajsutes, el bot lo tengo con 2 se queda con 2 y acepto la perdida y dejo atras querer tener la razón</t>
+    <t>PPA 103, a la estrategia no ingresamos por reglas. Acepto cada resultado con serenidad. Mi plan decide mis entradas, mi experto opera con dos órdenes y suelto la necesidad de tener la razón, porque el mercado sigue su curso y yo sigo el mío.</t>
+  </si>
+  <si>
+    <t>Mi plan se confirma en el mercado y yo lo sigo con calma: cada regla cumplida construye mi camino hacia la Incubación.</t>
   </si>
   <si>
     <t>Dia Semana</t>
@@ -1688,28 +1691,31 @@
         <v>-0.39</v>
       </c>
       <c r="I15" s="10">
-        <v>-2.2799999999999998</v>
+        <f>-2.28-0.11</f>
+        <v>-2.3899999999999997</v>
       </c>
       <c r="J15" s="10">
         <v>1</v>
       </c>
       <c r="K15" s="10">
         <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
-        <v>509.35</v>
+        <v>509.24</v>
       </c>
       <c r="L15" s="10"/>
       <c r="M15" s="14">
         <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
-        <v>-0.71150097465886952</v>
+        <v>-0.73294346978557501</v>
       </c>
       <c r="N15" s="12">
         <f>(K15-$C$2)/($C$2)*100</f>
-        <v>-2.0518441598399986</v>
+        <v>-2.0729971924156714</v>
       </c>
       <c r="O15" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="11"/>
+      <c r="P15" s="11" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
@@ -1757,31 +1763,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2022,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2059,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2231,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2317,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2335,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2354,7 +2360,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2388,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2422,7 +2428,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2456,7 +2462,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2474,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2493,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2511,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2530,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F23" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2563,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2581,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2600,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F25" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2634,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2668,7 +2674,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F27" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2702,7 +2708,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F28" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2720,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2739,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F29" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2757,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2776,7 +2782,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F30" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2809,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F31" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2843,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F32" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2877,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2911,7 +2917,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2945,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F35" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2979,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2997,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3016,7 +3022,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3034,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3052,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3086,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F39" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3120,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F40" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3154,7 +3160,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F41" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3188,7 +3194,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F42" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3222,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F43" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3256,7 +3262,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F44" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3289,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F45" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3323,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F46" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3357,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F47" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3391,7 +3397,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F48" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3425,7 +3431,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F49" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3459,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F50" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3493,7 +3499,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F51" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3526,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F52" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3560,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F53" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3594,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F54" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3628,7 +3634,7 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F55" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3662,7 +3668,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F56" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3696,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F57" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3730,7 +3736,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F58" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3763,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F59" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3797,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F60" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3831,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F61" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3865,7 +3871,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F62" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3899,7 +3905,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F63" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3933,7 +3939,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F64" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3967,7 +3973,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F65" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4000,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F66" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4034,7 +4040,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F67" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4068,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F68" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4102,7 +4108,7 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F69" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4136,7 +4142,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F70" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4170,7 +4176,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F71" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4204,7 +4210,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F72" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4237,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F73" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4271,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F74" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4305,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F75" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4339,7 +4345,7 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F76" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4373,7 +4379,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F77" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4407,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F78" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4441,7 +4447,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F79" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4474,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F80" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4508,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F81" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4542,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F82" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4576,7 +4582,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F83" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4610,7 +4616,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F84" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4644,7 +4650,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F85" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4678,7 +4684,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F86" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4711,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F87" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4745,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F88" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4779,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F89" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4813,7 +4819,7 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F90" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4847,7 +4853,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F91" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4881,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F92" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4915,7 +4921,7 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F93" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4948,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F94" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4982,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F95" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5016,7 +5022,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F96" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5050,7 +5056,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F97" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5084,7 +5090,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F98" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5118,7 +5124,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F99" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5152,7 +5158,7 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F100" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5185,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F101" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5219,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F102" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5253,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F103" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5287,7 +5293,7 @@
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F104" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5321,7 +5327,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F105" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5355,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F106" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5389,7 +5395,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F107" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5422,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F108" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5456,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F109" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5490,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F110" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5524,7 +5530,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F111" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5558,7 +5564,7 @@
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F112" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5592,7 +5598,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F113" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5626,7 +5632,7 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F114" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5659,7 +5665,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F115" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5693,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F116" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5727,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F117" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5761,7 +5767,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F118" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5795,7 +5801,7 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F119" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5829,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F120" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5863,7 +5869,7 @@
         <v>2</v>
       </c>
       <c r="E121" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F121" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5896,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F122" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5930,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F123" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5964,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F124" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5998,7 +6004,7 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F125" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6032,7 +6038,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F126" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6066,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F127" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6100,7 +6106,7 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F128" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6133,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F129" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6167,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F130" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6201,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F131" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6235,7 +6241,7 @@
         <v>2</v>
       </c>
       <c r="E132" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F132" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6269,7 +6275,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F133" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6303,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F134" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6337,7 +6343,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F135" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6370,7 +6376,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F136" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6404,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F137" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6438,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F138" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6472,7 +6478,7 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F139" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6506,7 +6512,7 @@
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F140" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6540,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F141" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6574,7 +6580,7 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F142" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6607,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F143" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6641,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F144" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6675,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F145" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6709,7 +6715,7 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F146" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6743,7 +6749,7 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F147" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6777,7 +6783,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F148" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6811,7 +6817,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F149" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6844,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F150" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6878,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F151" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6912,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F152" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6946,7 +6952,7 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F153" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6980,7 +6986,7 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F154" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7014,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F155" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7048,7 +7054,7 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F156" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7081,7 +7087,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F157" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7115,7 +7121,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F158" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7149,7 +7155,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F159" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7183,7 +7189,7 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F160" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7217,7 +7223,7 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F161" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7251,7 +7257,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F162" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7285,7 +7291,7 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F163" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7318,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F164" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7352,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F165" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7386,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F166" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7420,7 +7426,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F167" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7454,7 +7460,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F168" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7488,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F169" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7522,7 +7528,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F170" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7555,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F171" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7589,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F172" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7623,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F173" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7657,7 +7663,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F174" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7691,7 +7697,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F175" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7725,7 +7731,7 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F176" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7759,7 +7765,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F177" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7792,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F178" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7826,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F179" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7860,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F180" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7894,7 +7900,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F181" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7928,7 +7934,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F182" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7962,7 +7968,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F183" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7996,7 +8002,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F184" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8029,7 +8035,7 @@
         <v>0</v>
       </c>
       <c r="E185" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F185" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8063,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F186" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8097,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F187" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8131,7 +8137,7 @@
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F188" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8165,7 +8171,7 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F189" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8199,7 +8205,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F190" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8233,7 +8239,7 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F191" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8266,7 +8272,7 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F192" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8300,7 +8306,7 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F193" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8334,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F194" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8368,7 +8374,7 @@
         <v>2</v>
       </c>
       <c r="E195" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F195" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8402,7 +8408,7 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F196" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8436,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F197" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8470,7 +8476,7 @@
         <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F198" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8503,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F199" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8537,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F200" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8571,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F201" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8605,7 +8611,7 @@
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F202" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8639,7 +8645,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F203" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8673,7 +8679,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F204" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8707,7 +8713,7 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F205" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8740,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F206" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8774,7 +8780,7 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F207" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8808,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F208" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8842,7 +8848,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F209" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8876,7 +8882,7 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F210" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8910,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F211" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8944,7 +8950,7 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F212" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8977,7 +8983,7 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F213" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9011,7 +9017,7 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F214" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9045,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F215" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9079,7 +9085,7 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F216" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9113,7 +9119,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F217" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9147,7 +9153,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F218" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9181,7 +9187,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F219" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9214,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F220" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9248,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F221" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9282,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F222" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9316,7 +9322,7 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F223" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9350,7 +9356,7 @@
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F224" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9384,7 +9390,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F225" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9418,7 +9424,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F226" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9451,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F227" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9485,7 +9491,7 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F228" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9519,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F229" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9553,7 +9559,7 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F230" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9587,7 +9593,7 @@
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F231" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9621,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F232" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9655,7 +9661,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F233" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9688,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F234" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9722,7 +9728,7 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F235" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9756,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F236" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9790,7 +9796,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F237" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9824,7 +9830,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F238" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9858,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F239" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9892,7 +9898,7 @@
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F240" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9925,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F241" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9959,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="E242" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F242" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9993,7 +9999,7 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F243" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10027,7 +10033,7 @@
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F244" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10061,7 +10067,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F245" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10095,7 +10101,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F246" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10129,7 +10135,7 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F247" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10162,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="E248" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F248" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10196,7 +10202,7 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F249" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10230,7 +10236,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F250" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10264,7 +10270,7 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F251" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10298,7 +10304,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F252" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10332,7 +10338,7 @@
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F253" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10366,7 +10372,7 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F254" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10399,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F255" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10433,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F256" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10467,7 +10473,7 @@
         <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F257" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10501,7 +10507,7 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F258" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10535,7 +10541,7 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F259" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10569,7 +10575,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F260" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10603,7 +10609,7 @@
         <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F261" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10636,7 +10642,7 @@
         <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F262" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10670,7 +10676,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F263" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10704,7 +10710,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F264" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10738,7 +10744,7 @@
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F265" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10772,7 +10778,7 @@
         <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F266" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10806,7 +10812,7 @@
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F267" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10840,7 +10846,7 @@
         <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F268" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10873,7 +10879,7 @@
         <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F269" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10907,7 +10913,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F270" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10941,7 +10947,7 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F271" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10992,15 +10998,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -11008,7 +11014,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -11016,7 +11022,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -11024,7 +11030,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -11032,7 +11038,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -11040,7 +11046,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -11048,7 +11054,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -11079,31 +11085,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11132,12 +11138,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="17">
         <v>5.0000000000000001E-3</v>
@@ -11161,12 +11167,12 @@
         <v>0.4</v>
       </c>
       <c r="I3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11190,12 +11196,12 @@
         <v>0.5</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11219,12 +11225,12 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11248,12 +11254,12 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11277,7 +11283,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30619"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9A608E9-4926-412D-A281-A4900027C4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48FA1A1A-5991-4694-AC8F-16E356FCAB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="96">
   <si>
     <t>Fecha</t>
   </si>
@@ -1680,8 +1680,12 @@
         <f>K14+L14</f>
         <v>513</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="D15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>18</v>
+      </c>
       <c r="F15" s="10"/>
       <c r="G15" s="10">
         <v>-1.98</v>

--- a/Magic_Number.xlsx
+++ b/Magic_Number.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30621"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48FA1A1A-5991-4694-AC8F-16E356FCAB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6122CB7-6D2B-476A-B73C-2F7C7DC4D347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="98">
   <si>
     <t>Fecha</t>
   </si>
@@ -187,6 +187,12 @@
   </si>
   <si>
     <t>Mi plan se confirma en el mercado y yo lo sigo con calma: cada regla cumplida construye mi camino hacia la Incubación.</t>
+  </si>
+  <si>
+    <t>PA 64, no se ingresa por reglas claras de viernes</t>
+  </si>
+  <si>
+    <t>Elijo la claridad: mi plan guía cada decisión, y cada ajuste nace de la calma y de mis reglas.</t>
   </si>
   <si>
     <t>Dia Semana</t>
@@ -632,8 +638,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P15" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
-  <autoFilter ref="A1:P15" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3BD64674-65C8-4841-9ACB-40AEA98C620C}" name="Tabla13" displayName="Tabla13" ref="A1:P16" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23">
+  <autoFilter ref="A1:P16" xr:uid="{4A9E33D3-7020-4F9C-BD9E-F60D3EA3C645}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{B2179686-94A6-47CB-82BB-24954724055D}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="14" xr3:uid="{E37DBF04-766D-4AF7-9F73-CBD71B2EB08F}" name="Etapa "/>
@@ -1017,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84821E32-04A7-436B-A289-C562F3791E29}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="4" customWidth="1"/>
@@ -1721,6 +1727,52 @@
         <v>48</v>
       </c>
     </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="10">
+        <f>K15+L15</f>
+        <v>509.24</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10">
+        <f>Tabla13[[#This Row],[Balance Inicial ]]+Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]]</f>
+        <v>511.74</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="14">
+        <f>(Tabla13[[#This Row],[Estrategia]]+Tabla13[[#This Row],[Ajuste 1]]+Tabla13[[#This Row],[Ajuste 2]]+Tabla13[[#This Row],[Ajuste 3]]+Tabla13[[#This Row],[Ajuste 4]])/Tabla13[[#This Row],[Balance Inicial ]]*100</f>
+        <v>0.49092765690047907</v>
+      </c>
+      <c r="N16" s="12">
+        <f>(K16-$C$2)/($C$2)*100</f>
+        <v>-1.592246452059531</v>
+      </c>
+      <c r="O16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="P16" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="M1:P1048576">
     <cfRule type="cellIs" dxfId="25" priority="1" operator="lessThan">
@@ -1738,7 +1790,7 @@
           <x14:formula1>
             <xm:f>Etapas!$A$2:$A$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B15</xm:sqref>
+          <xm:sqref>B2:B16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1767,31 +1819,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2032,7 +2084,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2069,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2241,7 +2293,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2327,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F17" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2345,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2364,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F18" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2398,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F19" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2432,7 +2484,7 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2466,7 +2518,7 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F21" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2484,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -2503,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F22" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2521,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -2540,7 +2592,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F23" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2573,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F24" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2591,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2610,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F25" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2644,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F26" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2678,7 +2730,7 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F27" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2712,7 +2764,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F28" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2730,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2749,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F29" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2767,7 +2819,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2786,7 +2838,7 @@
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F30" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2819,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F31" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2853,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F32" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2887,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2921,7 +2973,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2955,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F35" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -2989,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F36" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3007,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -3026,7 +3078,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F37" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3044,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -3062,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F38" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3096,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F39" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3130,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F40" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3164,7 +3216,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F41" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3198,7 +3250,7 @@
         <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F42" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3232,7 +3284,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F43" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3266,7 +3318,7 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F44" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3299,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F45" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3333,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F46" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3367,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F47" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3401,7 +3453,7 @@
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F48" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3435,7 +3487,7 @@
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F49" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3469,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F50" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3503,7 +3555,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F51" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3536,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F52" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3570,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F53" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3604,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F54" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3638,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="E55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F55" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3672,7 +3724,7 @@
         <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F56" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3706,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F57" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3740,7 +3792,7 @@
         <v>2</v>
       </c>
       <c r="E58" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F58" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3773,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F59" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3807,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F60" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3841,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F61" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3875,7 +3927,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F62" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3909,7 +3961,7 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F63" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3943,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F64" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -3977,7 +4029,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F65" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4010,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F66" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4044,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F67" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4078,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F68" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4112,7 +4164,7 @@
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F69" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4146,7 +4198,7 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F70" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4180,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F71" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4214,7 +4266,7 @@
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F72" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4247,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F73" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4281,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F74" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4315,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F75" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4349,7 +4401,7 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F76" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4383,7 +4435,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F77" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4417,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F78" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4451,7 +4503,7 @@
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F79" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4484,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F80" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4518,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F81" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4552,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F82" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4586,7 +4638,7 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F83" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4620,7 +4672,7 @@
         <v>2</v>
       </c>
       <c r="E84" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F84" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4654,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F85" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4688,7 +4740,7 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F86" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4721,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F87" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4755,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F88" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4789,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F89" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4823,7 +4875,7 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F90" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4857,7 +4909,7 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F91" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4891,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F92" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4925,7 +4977,7 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F93" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4958,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F94" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -4992,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F95" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5026,7 +5078,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F96" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5060,7 +5112,7 @@
         <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F97" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5094,7 +5146,7 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F98" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5128,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F99" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5162,7 +5214,7 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F100" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5195,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="E101" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F101" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5229,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="E102" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F102" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5263,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F103" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5297,7 +5349,7 @@
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F104" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5331,7 +5383,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F105" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5365,7 +5417,7 @@
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F106" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5399,7 +5451,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F107" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5432,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="E108" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F108" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5466,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F109" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5500,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="E110" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F110" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5534,7 +5586,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F111" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5568,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="E112" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F112" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5602,7 +5654,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F113" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5636,7 +5688,7 @@
         <v>2</v>
       </c>
       <c r="E114" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F114" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5669,7 +5721,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F115" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5703,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F116" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5737,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F117" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5771,7 +5823,7 @@
         <v>2</v>
       </c>
       <c r="E118" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F118" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5805,7 +5857,7 @@
         <v>2</v>
       </c>
       <c r="E119" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F119" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5839,7 +5891,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F120" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5873,7 +5925,7 @@
         <v>2</v>
       </c>
       <c r="E121" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F121" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5906,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F122" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5940,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="E123" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F123" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -5974,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F124" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6008,7 +6060,7 @@
         <v>2</v>
       </c>
       <c r="E125" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F125" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6042,7 +6094,7 @@
         <v>2</v>
       </c>
       <c r="E126" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F126" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6076,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="E127" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F127" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6110,7 +6162,7 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F128" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6143,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F129" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6177,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="E130" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F130" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6211,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F131" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6245,7 +6297,7 @@
         <v>2</v>
       </c>
       <c r="E132" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F132" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6279,7 +6331,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F133" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6313,7 +6365,7 @@
         <v>1</v>
       </c>
       <c r="E134" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F134" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6347,7 +6399,7 @@
         <v>2</v>
       </c>
       <c r="E135" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F135" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6380,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="E136" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F136" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6414,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="E137" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F137" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6448,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="E138" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F138" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6482,7 +6534,7 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F139" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6516,7 +6568,7 @@
         <v>2</v>
       </c>
       <c r="E140" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F140" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6550,7 +6602,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F141" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6584,7 +6636,7 @@
         <v>2</v>
       </c>
       <c r="E142" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F142" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6617,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="E143" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F143" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6651,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="E144" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F144" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6685,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="E145" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F145" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6719,7 +6771,7 @@
         <v>2</v>
       </c>
       <c r="E146" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F146" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6753,7 +6805,7 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F147" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6787,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F148" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6821,7 +6873,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F149" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6854,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="E150" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F150" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6888,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="E151" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F151" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6922,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F152" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6956,7 +7008,7 @@
         <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F153" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -6990,7 +7042,7 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F154" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7024,7 +7076,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F155" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7058,7 +7110,7 @@
         <v>2</v>
       </c>
       <c r="E156" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F156" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7091,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F157" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7125,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F158" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7159,7 +7211,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F159" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7193,7 +7245,7 @@
         <v>2</v>
       </c>
       <c r="E160" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F160" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7227,7 +7279,7 @@
         <v>2</v>
       </c>
       <c r="E161" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F161" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7261,7 +7313,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F162" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7295,7 +7347,7 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F163" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7328,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="E164" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F164" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7362,7 +7414,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F165" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7396,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F166" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7430,7 +7482,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F167" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7464,7 +7516,7 @@
         <v>2</v>
       </c>
       <c r="E168" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F168" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7498,7 +7550,7 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F169" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7532,7 +7584,7 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F170" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7565,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="E171" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F171" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7599,7 +7651,7 @@
         <v>0</v>
       </c>
       <c r="E172" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F172" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7633,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="E173" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F173" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7667,7 +7719,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F174" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7701,7 +7753,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F175" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7735,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F176" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7769,7 +7821,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F177" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7802,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="E178" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F178" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7836,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="E179" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F179" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7870,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F180" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7904,7 +7956,7 @@
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F181" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7938,7 +7990,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F182" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -7972,7 +8024,7 @@
         <v>1</v>
       </c>
       <c r="E183" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F183" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8006,7 +8058,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F184" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8039,7 +8091,7 @@
         <v>0</v>
       </c>
       <c r="E185" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F185" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8073,7 +8125,7 @@
         <v>0</v>
       </c>
       <c r="E186" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F186" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8107,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="E187" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F187" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8141,7 +8193,7 @@
         <v>2</v>
       </c>
       <c r="E188" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F188" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8175,7 +8227,7 @@
         <v>2</v>
       </c>
       <c r="E189" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F189" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8209,7 +8261,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F190" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8243,7 +8295,7 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F191" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8276,7 +8328,7 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F192" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8310,7 +8362,7 @@
         <v>0</v>
       </c>
       <c r="E193" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F193" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8344,7 +8396,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F194" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8378,7 +8430,7 @@
         <v>2</v>
       </c>
       <c r="E195" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F195" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8412,7 +8464,7 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F196" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8446,7 +8498,7 @@
         <v>1</v>
       </c>
       <c r="E197" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F197" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8480,7 +8532,7 @@
         <v>2</v>
       </c>
       <c r="E198" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F198" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8513,7 +8565,7 @@
         <v>0</v>
       </c>
       <c r="E199" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F199" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8547,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F200" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8581,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F201" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8615,7 +8667,7 @@
         <v>2</v>
       </c>
       <c r="E202" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F202" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8649,7 +8701,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F203" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8683,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F204" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8717,7 +8769,7 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F205" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8750,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F206" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8784,7 +8836,7 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F207" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8818,7 +8870,7 @@
         <v>0</v>
       </c>
       <c r="E208" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F208" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8852,7 +8904,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F209" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8886,7 +8938,7 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F210" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8920,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="E211" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F211" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8954,7 +9006,7 @@
         <v>2</v>
       </c>
       <c r="E212" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F212" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -8987,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="E213" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F213" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9021,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="E214" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F214" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9055,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="E215" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F215" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9089,7 +9141,7 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F216" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9123,7 +9175,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F217" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9157,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F218" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9191,7 +9243,7 @@
         <v>2</v>
       </c>
       <c r="E219" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F219" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9224,7 +9276,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F220" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9258,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="E221" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F221" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9292,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="E222" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F222" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9326,7 +9378,7 @@
         <v>2</v>
       </c>
       <c r="E223" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F223" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9360,7 +9412,7 @@
         <v>2</v>
       </c>
       <c r="E224" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F224" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9394,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F225" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9428,7 +9480,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F226" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9461,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="E227" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F227" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9495,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="E228" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F228" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9529,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="E229" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F229" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9563,7 +9615,7 @@
         <v>2</v>
       </c>
       <c r="E230" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F230" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9597,7 +9649,7 @@
         <v>2</v>
       </c>
       <c r="E231" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F231" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9631,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="E232" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F232" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9665,7 +9717,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F233" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9698,7 +9750,7 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F234" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9732,7 +9784,7 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F235" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9766,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F236" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9800,7 +9852,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F237" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9834,7 +9886,7 @@
         <v>2</v>
       </c>
       <c r="E238" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F238" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9868,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="E239" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F239" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9902,7 +9954,7 @@
         <v>2</v>
       </c>
       <c r="E240" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F240" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9935,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="E241" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F241" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -9969,7 +10021,7 @@
         <v>0</v>
       </c>
       <c r="E242" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F242" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10003,7 +10055,7 @@
         <v>0</v>
       </c>
       <c r="E243" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F243" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10037,7 +10089,7 @@
         <v>2</v>
       </c>
       <c r="E244" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F244" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10071,7 +10123,7 @@
         <v>2</v>
       </c>
       <c r="E245" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F245" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10105,7 +10157,7 @@
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F246" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10139,7 +10191,7 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F247" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10172,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="E248" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F248" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10206,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="E249" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F249" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10240,7 +10292,7 @@
         <v>0</v>
       </c>
       <c r="E250" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F250" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10274,7 +10326,7 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F251" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10308,7 +10360,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F252" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10342,7 +10394,7 @@
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F253" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10376,7 +10428,7 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F254" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10409,7 +10461,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F255" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10443,7 +10495,7 @@
         <v>0</v>
       </c>
       <c r="E256" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F256" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10477,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="E257" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F257" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10511,7 +10563,7 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F258" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10545,7 +10597,7 @@
         <v>2</v>
       </c>
       <c r="E259" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F259" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10579,7 +10631,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F260" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10613,7 +10665,7 @@
         <v>2</v>
       </c>
       <c r="E261" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F261" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10646,7 +10698,7 @@
         <v>0</v>
       </c>
       <c r="E262" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F262" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10680,7 +10732,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F263" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10714,7 +10766,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F264" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10748,7 +10800,7 @@
         <v>2</v>
       </c>
       <c r="E265" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F265" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10782,7 +10834,7 @@
         <v>2</v>
       </c>
       <c r="E266" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F266" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10816,7 +10868,7 @@
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F267" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10850,7 +10902,7 @@
         <v>2</v>
       </c>
       <c r="E268" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F268" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10883,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="E269" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F269" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10917,7 +10969,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F270" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -10951,7 +11003,7 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F271" s="17">
         <f>_xlfn.XLOOKUP(Tabla3[[#This Row],[Etapa]],Etapas!A:A,Etapas!B:B)</f>
@@ -11002,15 +11054,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -11018,7 +11070,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -11026,7 +11078,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -11034,7 +11086,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -11042,7 +11094,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -11050,7 +11102,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -11058,7 +11110,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -11089,31 +11141,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -11142,12 +11194,12 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="17">
         <v>5.0000000000000001E-3</v>
@@ -11171,12 +11223,12 @@
         <v>0.4</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11200,12 +11252,12 @@
         <v>0.5</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11229,12 +11281,12 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11258,12 +11310,12 @@
         <v>0.7</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="17">
         <v>3.5000000000000001E-3</v>
@@ -11287,7 +11339,7 @@
         <v>0.8</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
